--- a/kirill/outputs/hazam-tracking-dashboard.xlsx
+++ b/kirill/outputs/hazam-tracking-dashboard.xlsx
@@ -4,11 +4,14 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="חאזם" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דודו" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="חיים" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סטאס" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -17,12 +20,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * \-??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="168" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="40">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -263,8 +268,43 @@
       <color rgb="FF595959"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10.5"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -318,8 +358,38 @@
         <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092D050"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -356,6 +426,64 @@
         <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -367,7 +495,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -643,6 +771,45 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="36" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="36" fillId="13" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="36" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="36" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="35" fillId="14" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="35" fillId="14" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="36" fillId="10" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="15" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="35" fillId="15" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="35" fillId="15" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="32" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2270,36 +2437,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="B3" authorId="0" shapeId="0">
-      <text>
-        <t>שדה זה מוזן ידנית ואינו מחושב אוטומטית - זהו התאריך היחיד בגיליון שאינו נוסחה חיה. נכון להיום (16/08/26) יום הבדיקה נקבע לאמצע החודש (15/08/26). כל שאר החישובים (ימים שעברו, קצב, אחוז ביצוע) מתעדכנים אוטומטית לפי תאריך זה - כדי לבדוק תאריך אחר, פשוט לעדכן תא זה.</t>
-      </text>
-    </comment>
-    <comment ref="B6" authorId="0" shapeId="0">
-      <text>
-        <t>ספירה חיה של ימי ראשון עד חמישי (ללא שישי-שבת) בכל טווח החודש (מתחילתו עד סופו). שיטה: WEEKDAY בברירת המחדל (1=ראשון...7=שבת), וספירת כל יום שבו weekday&lt;6 (כלומר לא שישי ולא שבת) בעזרת SUMPRODUCT+ROW(INDIRECT(...)). לאוגוסט 2026 התוצאה היא 22 ימים.</t>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>אותה שיטת ספירה כמו B6, אך רק מתחילת החודש ועד יום הבדיקה (B3). לבדיקה ב-15/08/26 התוצאה היא 10 ימים.</t>
-      </text>
-    </comment>
-    <comment ref="C19" authorId="0" shapeId="0">
-      <text>
-        <t>פער בנתוני המקור: לא נמצא יעד חודשי מוגדר לקטגוריה 'חנויות ספורט' בקובץ המקור (hazam-tracking-source.xlsx, C11 היה ריק). יש להשלים ידנית מול הסוכן/המנהל. עד להשלמה, אחוז ביצוע וקצב % לקטגוריה זו יוצגו כריק.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
@@ -2562,7 +2699,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FF808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2615,7 +2752,7 @@
           <t>תחילת החודש הרלוונטי:</t>
         </is>
       </c>
-      <c r="B4" s="52" t="n">
+      <c t="n" r="B4" s="52">
         <f>EOMONTH(B3,-1)+1</f>
         <v>46235</v>
       </c>
@@ -2626,7 +2763,7 @@
           <t>סוף החודש הרלוונטי:</t>
         </is>
       </c>
-      <c r="B5" s="52" t="n">
+      <c t="n" r="B5" s="52">
         <f>EOMONTH(B3,0)</f>
         <v>46265</v>
       </c>
@@ -2637,7 +2774,7 @@
           <t>סה"כ ימי א'-ה' בחודש:</t>
         </is>
       </c>
-      <c r="B6" s="54" t="n">
+      <c t="n" r="B6" s="54">
         <f>SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B5)))&lt;6)*1)</f>
         <v>22</v>
       </c>
@@ -2648,7 +2785,7 @@
           <t>ימי א'-ה' שעברו (מ-1 בחודש עד יום הבדיקה):</t>
         </is>
       </c>
-      <c r="B7" s="54" t="n">
+      <c t="n" r="B7" s="54">
         <f>SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B3)))&lt;6)*1)</f>
         <v>10</v>
       </c>
@@ -2739,23 +2876,23 @@
       <c r="E11" s="60" t="n">
         <v>4595</v>
       </c>
-      <c r="F11" s="61" t="n">
+      <c t="n" r="F11" s="61">
         <f>D11+E11</f>
         <v>24608.1</v>
       </c>
-      <c r="G11" s="62" t="n">
+      <c t="n" r="G11" s="62">
         <f>IFERROR(F11/C11,"")</f>
         <v>0.225762385321101</v>
       </c>
-      <c r="H11" s="61" t="n">
+      <c t="n" r="H11" s="61">
         <f>IF(C11="","",C11-F11)</f>
         <v>84391.9</v>
       </c>
-      <c r="I11" s="61" t="n">
+      <c t="n" r="I11" s="61">
         <f>IFERROR((F11/$B$7)*$B$6,"")</f>
         <v>54137.82</v>
       </c>
-      <c r="J11" s="62" t="n">
+      <c t="n" r="J11" s="62">
         <f>IFERROR(I11/C11,"")</f>
         <v>0.496677247706422</v>
       </c>
@@ -2775,23 +2912,23 @@
       <c r="E12" s="60" t="n">
         <v>646</v>
       </c>
-      <c r="F12" s="61" t="n">
+      <c t="n" r="F12" s="61">
         <f>D12+E12</f>
         <v>10455.2</v>
       </c>
-      <c r="G12" s="62" t="n">
+      <c t="n" r="G12" s="62">
         <f>IFERROR(F12/C12,"")</f>
         <v>0.417040287195852</v>
       </c>
-      <c r="H12" s="61" t="n">
+      <c t="n" r="H12" s="61">
         <f>IF(C12="","",C12-F12)</f>
         <v>14614.8</v>
       </c>
-      <c r="I12" s="61" t="n">
+      <c t="n" r="I12" s="61">
         <f>IFERROR((F12/$B$7)*$B$6,"")</f>
         <v>23001.44</v>
       </c>
-      <c r="J12" s="62" t="n">
+      <c t="n" r="J12" s="62">
         <f>IFERROR(I12/C12,"")</f>
         <v>0.917488631830874</v>
       </c>
@@ -2809,23 +2946,23 @@
         <v>50294</v>
       </c>
       <c r="E13" s="60" t="n"/>
-      <c r="F13" s="61" t="n">
+      <c t="n" r="F13" s="61">
         <f>D13+E13</f>
         <v>50294</v>
       </c>
-      <c r="G13" s="62" t="n">
+      <c t="n" r="G13" s="62">
         <f>IFERROR(F13/C13,"")</f>
         <v>0.419466221851543</v>
       </c>
-      <c r="H13" s="61" t="n">
+      <c t="n" r="H13" s="61">
         <f>IF(C13="","",C13-F13)</f>
         <v>69606</v>
       </c>
-      <c r="I13" s="61" t="n">
+      <c t="n" r="I13" s="61">
         <f>IFERROR((F13/$B$7)*$B$6,"")</f>
         <v>110646.8</v>
       </c>
-      <c r="J13" s="62" t="n">
+      <c t="n" r="J13" s="62">
         <f>IFERROR(I13/C13,"")</f>
         <v>0.922825688073394</v>
       </c>
@@ -2836,35 +2973,35 @@
           <t>סה"כ</t>
         </is>
       </c>
-      <c r="C14" s="64" t="n">
+      <c t="n" r="C14" s="64">
         <f>SUM(C11:C13)</f>
         <v>253970</v>
       </c>
-      <c r="D14" s="64" t="n">
+      <c t="n" r="D14" s="64">
         <f>SUM(D11:D13)</f>
         <v>80116.3</v>
       </c>
-      <c r="E14" s="64" t="n">
+      <c t="n" r="E14" s="64">
         <f>SUM(E11:E13)</f>
         <v>5241</v>
       </c>
-      <c r="F14" s="64" t="n">
+      <c t="n" r="F14" s="64">
         <f>SUM(F11:F13)</f>
         <v>85357.3</v>
       </c>
-      <c r="G14" s="65" t="n">
+      <c t="n" r="G14" s="65">
         <f>IFERROR(F14/C14,"")</f>
         <v>0.3360920581171</v>
       </c>
-      <c r="H14" s="64" t="n">
+      <c t="n" r="H14" s="64">
         <f>IF(C14="","",C14-F14)</f>
         <v>168612.7</v>
       </c>
-      <c r="I14" s="64" t="n">
+      <c t="n" r="I14" s="64">
         <f>IFERROR((F14/$B$7)*$B$6,"")</f>
         <v>187786.06</v>
       </c>
-      <c r="J14" s="65" t="n">
+      <c t="n" r="J14" s="65">
         <f>IFERROR(I14/C14,"")</f>
         <v>0.739402527857621</v>
       </c>
@@ -2882,23 +3019,23 @@
         <v>19629</v>
       </c>
       <c r="E15" s="60" t="n"/>
-      <c r="F15" s="61" t="n">
+      <c t="n" r="F15" s="61">
         <f>D15+E15</f>
         <v>19629</v>
       </c>
-      <c r="G15" s="62" t="n">
+      <c t="n" r="G15" s="62">
         <f>IFERROR(F15/C15,"")</f>
         <v>0.413616537075669</v>
       </c>
-      <c r="H15" s="61" t="n">
+      <c t="n" r="H15" s="61">
         <f>IF(C15="","",C15-F15)</f>
         <v>27828</v>
       </c>
-      <c r="I15" s="61" t="n">
+      <c t="n" r="I15" s="61">
         <f>IFERROR((F15/$B$7)*$B$6,"")</f>
         <v>43183.8</v>
       </c>
-      <c r="J15" s="62" t="n">
+      <c t="n" r="J15" s="62">
         <f>IFERROR(I15/C15,"")</f>
         <v>0.909956381566471</v>
       </c>
@@ -2909,7 +3046,7 @@
           <t>מכוני פיזוטרפיה</t>
         </is>
       </c>
-      <c r="C16" s="60" t="n">
+      <c t="n" r="C16" s="60">
         <f>16734+302</f>
         <v>17036</v>
       </c>
@@ -2917,23 +3054,23 @@
         <v>5352</v>
       </c>
       <c r="E16" s="60" t="n"/>
-      <c r="F16" s="61" t="n">
+      <c t="n" r="F16" s="61">
         <f>D16+E16</f>
         <v>5352</v>
       </c>
-      <c r="G16" s="62" t="n">
+      <c t="n" r="G16" s="62">
         <f>IFERROR(F16/C16,"")</f>
         <v>0.314158253111059</v>
       </c>
-      <c r="H16" s="61" t="n">
+      <c t="n" r="H16" s="61">
         <f>IF(C16="","",C16-F16)</f>
         <v>11684</v>
       </c>
-      <c r="I16" s="61" t="n">
+      <c t="n" r="I16" s="61">
         <f>IFERROR((F16/$B$7)*$B$6,"")</f>
         <v>11774.4</v>
       </c>
-      <c r="J16" s="62" t="n">
+      <c t="n" r="J16" s="62">
         <f>IFERROR(I16/C16,"")</f>
         <v>0.69114815684433</v>
       </c>
@@ -2953,23 +3090,23 @@
       <c r="E17" s="60" t="n">
         <v>302</v>
       </c>
-      <c r="F17" s="61" t="n">
+      <c t="n" r="F17" s="61">
         <f>D17+E17</f>
         <v>6928.4</v>
       </c>
-      <c r="G17" s="62" t="n">
+      <c t="n" r="G17" s="62">
         <f>IFERROR(F17/C17,"")</f>
         <v>0.317816513761468</v>
       </c>
-      <c r="H17" s="61" t="n">
+      <c t="n" r="H17" s="61">
         <f>IF(C17="","",C17-F17)</f>
         <v>14871.6</v>
       </c>
-      <c r="I17" s="61" t="n">
+      <c t="n" r="I17" s="61">
         <f>IFERROR((F17/$B$7)*$B$6,"")</f>
         <v>15242.48</v>
       </c>
-      <c r="J17" s="62" t="n">
+      <c t="n" r="J17" s="62">
         <f>IFERROR(I17/C17,"")</f>
         <v>0.699196330275229</v>
       </c>
@@ -2987,23 +3124,23 @@
         <v>0</v>
       </c>
       <c r="E18" s="60" t="n"/>
-      <c r="F18" s="61" t="n">
+      <c t="n" r="F18" s="61">
         <f>D18+E18</f>
         <v>0</v>
       </c>
-      <c r="G18" s="62" t="n">
+      <c t="n" r="G18" s="62">
         <f>IFERROR(F18/C18,"")</f>
         <v>0</v>
       </c>
-      <c r="H18" s="61" t="n">
+      <c t="n" r="H18" s="61">
         <f>IF(C18="","",C18-F18)</f>
         <v>6250</v>
       </c>
-      <c r="I18" s="61" t="n">
+      <c t="n" r="I18" s="61">
         <f>IFERROR((F18/$B$7)*$B$6,"")</f>
         <v>0</v>
       </c>
-      <c r="J18" s="62" t="n">
+      <c t="n" r="J18" s="62">
         <f>IFERROR(I18/C18,"")</f>
         <v>0</v>
       </c>
@@ -3019,23 +3156,23 @@
         <v>1276</v>
       </c>
       <c r="E19" s="60" t="n"/>
-      <c r="F19" s="61" t="n">
+      <c t="n" r="F19" s="61">
         <f>D19+E19</f>
         <v>1276</v>
       </c>
-      <c r="G19" s="62" t="str">
+      <c t="str" r="G19" s="62">
         <f>IFERROR(F19/C19,"")</f>
         <v/>
       </c>
-      <c r="H19" s="61" t="str">
+      <c t="str" r="H19" s="61">
         <f>IF(C19="","",C19-F19)</f>
         <v/>
       </c>
-      <c r="I19" s="61" t="n">
+      <c t="n" r="I19" s="61">
         <f>IFERROR((F19/$B$7)*$B$6,"")</f>
         <v>2807.2</v>
       </c>
-      <c r="J19" s="62" t="str">
+      <c t="str" r="J19" s="62">
         <f>IFERROR(I19/C19,"")</f>
         <v/>
       </c>
@@ -3047,35 +3184,35 @@
           <t>סה"כ</t>
         </is>
       </c>
-      <c r="C20" s="64" t="n">
+      <c t="n" r="C20" s="64">
         <f>SUM(C15:C19)</f>
         <v>92543</v>
       </c>
-      <c r="D20" s="64" t="n">
+      <c t="n" r="D20" s="64">
         <f>SUM(D15:D19)</f>
         <v>32883.4</v>
       </c>
-      <c r="E20" s="64" t="n">
+      <c t="n" r="E20" s="64">
         <f>SUM(E15:E19)</f>
         <v>302</v>
       </c>
-      <c r="F20" s="64" t="n">
+      <c t="n" r="F20" s="64">
         <f>SUM(F15:F19)</f>
         <v>33185.4</v>
       </c>
-      <c r="G20" s="65" t="n">
+      <c t="n" r="G20" s="65">
         <f>IFERROR(F20/C20,"")</f>
         <v>0.358594383151616</v>
       </c>
-      <c r="H20" s="64" t="n">
+      <c t="n" r="H20" s="64">
         <f>IF(C20="","",C20-F20)</f>
         <v>59357.6</v>
       </c>
-      <c r="I20" s="64" t="n">
+      <c t="n" r="I20" s="64">
         <f>IFERROR((F20/$B$7)*$B$6,"")</f>
         <v>73007.88</v>
       </c>
-      <c r="J20" s="65" t="n">
+      <c t="n" r="J20" s="65">
         <f>IFERROR(I20/C20,"")</f>
         <v>0.788907642933555</v>
       </c>
@@ -3087,39 +3224,40 @@
           <t>סה"כ כללי</t>
         </is>
       </c>
-      <c r="C21" s="69" t="n">
+      <c t="n" r="C21" s="69">
         <f>C14+C20</f>
         <v>346513</v>
       </c>
-      <c r="D21" s="69" t="n">
+      <c t="n" r="D21" s="69">
         <f>D14+D20</f>
         <v>112999.7</v>
       </c>
-      <c r="E21" s="69" t="n">
+      <c t="n" r="E21" s="69">
         <f>E14+E20</f>
         <v>5543</v>
       </c>
-      <c r="F21" s="69" t="n">
+      <c t="n" r="F21" s="69">
         <f>F14+F20</f>
         <v>118542.7</v>
       </c>
-      <c r="G21" s="70" t="n">
+      <c t="n" r="G21" s="70">
         <f>IFERROR(F21/C21,"")</f>
         <v>0.342101739328683</v>
       </c>
-      <c r="H21" s="69" t="n">
+      <c t="n" r="H21" s="69">
         <f>IF(C21="","",C21-F21)</f>
         <v>227970.3</v>
       </c>
-      <c r="I21" s="69" t="n">
+      <c t="n" r="I21" s="69">
         <f>IFERROR((F21/$B$7)*$B$6,"")</f>
         <v>260793.94</v>
       </c>
-      <c r="J21" s="70" t="n">
+      <c t="n" r="J21" s="70">
         <f>IFERROR(I21/C21,"")</f>
         <v>0.752623826523103</v>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="19.5" customHeight="1" s="49">
       <c r="A23" s="71" t="inlineStr">
         <is>
@@ -3134,30 +3272,44 @@
           <t>ימים שנותרו (א'-ה', עד סוף החודש)</t>
         </is>
       </c>
+      <c r="B25" s="93" t="n"/>
+      <c r="C25" s="94" t="n"/>
       <c r="D25" s="72" t="inlineStr">
         <is>
           <t>יעד יומי נדרש להשלמה (₪)</t>
         </is>
       </c>
+      <c r="E25" s="93" t="n"/>
+      <c r="F25" s="94" t="n"/>
       <c r="G25" s="72" t="inlineStr">
         <is>
           <t>אחוז ביצוע נוכחי (מתוך היעד הכולל)</t>
         </is>
       </c>
+      <c r="H25" s="93" t="n"/>
+      <c r="I25" s="93" t="n"/>
+      <c r="J25" s="94" t="n"/>
     </row>
     <row r="26" ht="26" customHeight="1" s="49">
-      <c r="A26" s="73" t="n">
+      <c t="n" r="A26" s="73">
         <f>IFERROR(B6-B7,"—")</f>
         <v>12</v>
       </c>
-      <c r="D26" s="74" t="n">
+      <c r="B26" s="93" t="n"/>
+      <c r="C26" s="94" t="n"/>
+      <c t="n" r="D26" s="74">
         <f>IFERROR(H21/(B6-B7),"—")</f>
         <v>18997.525</v>
       </c>
-      <c r="G26" s="75" t="n">
+      <c r="E26" s="93" t="n"/>
+      <c r="F26" s="94" t="n"/>
+      <c t="n" r="G26" s="75">
         <f>IFERROR((D21+E21)/C21,"—")</f>
         <v>0.342101739328683</v>
       </c>
+      <c r="H26" s="93" t="n"/>
+      <c r="I26" s="93" t="n"/>
+      <c r="J26" s="94" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="49"/>
     <row r="28" ht="28" customHeight="1" s="49">
@@ -3180,6 +3332,641 @@
     <row r="39" ht="15" customHeight="1" s="49"/>
     <row r="40" ht="39.75" customHeight="1" s="49"/>
     <row r="41" ht="18" customHeight="1" s="49"/>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="A11:A19"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A26:C26"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="2">
+      <formula>0.33</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="3">
+      <formula>0.66</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="4">
+      <formula>0.66</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="49" min="1" max="1"/>
+    <col width="22" customWidth="1" style="49" min="2" max="2"/>
+    <col width="13" customWidth="1" style="49" min="3" max="3"/>
+    <col width="15" customWidth="1" style="49" min="4" max="4"/>
+    <col width="13" customWidth="1" style="49" min="5" max="5"/>
+    <col width="16" customWidth="1" style="49" min="6" max="6"/>
+    <col width="13" customWidth="1" style="49" min="7" max="7"/>
+    <col width="16" customWidth="1" style="49" min="8" max="8"/>
+    <col width="16" customWidth="1" style="49" min="9" max="9"/>
+    <col width="10" customWidth="1" style="49" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="95" t="inlineStr">
+        <is>
+          <t>מעקב ביצועי סוכן דודו</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="96" t="inlineStr">
+        <is>
+          <t>תאריך חישוב:</t>
+        </is>
+      </c>
+      <c r="B2" s="97" t="n">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="96" t="inlineStr">
+        <is>
+          <t>יום בדיקה (קלט ידני):</t>
+        </is>
+      </c>
+      <c r="B3" s="98" t="n">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="96" t="inlineStr">
+        <is>
+          <t>תחילת החודש הרלוונטי:</t>
+        </is>
+      </c>
+      <c t="n" r="B4" s="97">
+        <f>EOMONTH(B3,-1)+1</f>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="96" t="inlineStr">
+        <is>
+          <t>סוף החודש הרלוונטי:</t>
+        </is>
+      </c>
+      <c t="n" r="B5" s="97">
+        <f>EOMONTH(B3,0)</f>
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="96" t="inlineStr">
+        <is>
+          <t>סה"כ ימי א'-ה' בחודש:</t>
+        </is>
+      </c>
+      <c t="n" r="B6" s="99">
+        <f>SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B5)))&lt;6)*1)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="96" t="inlineStr">
+        <is>
+          <t>ימי א'-ה' שעברו (מ-1 בחודש עד יום הבדיקה):</t>
+        </is>
+      </c>
+      <c t="n" r="B7" s="99">
+        <f>SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B3)))&lt;6)*1)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1" s="49">
+      <c r="A8" s="100" t="inlineStr">
+        <is>
+          <t>הערה: עמודות D ('מכירות') ו-E ('פתוחות') הן צילום מצב (snapshot) של הערכים המחושבים (קאש) שכבר קיימים בקובץ המקור שהועלה (agents-tracking-source-full.xlsx, גיליון 'דודו'), שם הם תוצאה של נוסחאות פנימיות מול גיליונות 'מכירות'/'פתוחות' באותו קובץ. הועתקו לכאן כערכים קשיחים (לא לינק חי), בהתאם לאותה שיטה שבה נבנה גיליון חאזם. לתשומת לב - פער בנתוני המקור: לא נמצא יעד חודשי (עמודה C) לקטגוריות: מכוני פיזוטרפיה; חנויות ספורט. עד להשלמה ידנית, אחוז ביצוע וקצב % לקטגוריות אלה יוצגו כריק.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" s="49">
+      <c r="A9" s="101" t="inlineStr">
+        <is>
+          <t>גיליון זה = נתוני מקור וחישוב (Working Data): כל הנוסחאות, המקור וה-snapshot המלאים נמצאים כאן. לתצוגת סיכום ויזואלית עם גרפים למנהל  ⇦  עבור לגיליון DASHBOARD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="31.5" customHeight="1" s="49">
+      <c r="A10" s="102" t="inlineStr">
+        <is>
+          <t>סוכן</t>
+        </is>
+      </c>
+      <c r="B10" s="102" t="inlineStr">
+        <is>
+          <t>קטגוריה</t>
+        </is>
+      </c>
+      <c r="C10" s="102" t="inlineStr">
+        <is>
+          <t>יעד חודשי (₪)</t>
+        </is>
+      </c>
+      <c r="D10" s="102" t="inlineStr">
+        <is>
+          <t>מכירות (snapshot)</t>
+        </is>
+      </c>
+      <c r="E10" s="102" t="inlineStr">
+        <is>
+          <t>פתוחות (snapshot)</t>
+        </is>
+      </c>
+      <c r="F10" s="102" t="inlineStr">
+        <is>
+          <t>מכירות עד לבדיקה (₪)</t>
+        </is>
+      </c>
+      <c r="G10" s="102" t="inlineStr">
+        <is>
+          <t>אחוז ביצוע לפי יעד</t>
+        </is>
+      </c>
+      <c r="H10" s="102" t="inlineStr">
+        <is>
+          <t>כמה נשאר לסיום החודש (₪)</t>
+        </is>
+      </c>
+      <c r="I10" s="102" t="inlineStr">
+        <is>
+          <t>קצב אומדן סוף חודש (₪)</t>
+        </is>
+      </c>
+      <c r="J10" s="102" t="inlineStr">
+        <is>
+          <t>קצב %</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="103" t="inlineStr">
+        <is>
+          <t>דודו</t>
+        </is>
+      </c>
+      <c r="B11" s="104" t="inlineStr">
+        <is>
+          <t>בתי מרקחת פרטיים</t>
+        </is>
+      </c>
+      <c r="C11" s="105" t="n">
+        <v>45780</v>
+      </c>
+      <c r="D11" s="105" t="n">
+        <v>28518.9</v>
+      </c>
+      <c r="E11" s="105" t="n">
+        <v>885</v>
+      </c>
+      <c t="n" r="F11" s="106">
+        <f>D11+E11</f>
+        <v>29403.9</v>
+      </c>
+      <c t="n" r="G11" s="107">
+        <f>IFERROR(F11/C11,"")</f>
+        <v>0.642287024901704</v>
+      </c>
+      <c t="n" r="H11" s="106">
+        <f>IF(C11="","",C11-F11)</f>
+        <v>16376.1</v>
+      </c>
+      <c t="n" r="I11" s="106">
+        <f>IFERROR((F11/$B$7)*$B$6,"")</f>
+        <v>64688.58</v>
+      </c>
+      <c t="n" r="J11" s="107">
+        <f>IFERROR(I11/C11,"")</f>
+        <v>1.41303145478375</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="104" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C12" s="105" t="n">
+        <v>25070</v>
+      </c>
+      <c r="D12" s="105" t="n">
+        <v>5330.1</v>
+      </c>
+      <c r="E12" s="105" t="n">
+        <v>320</v>
+      </c>
+      <c t="n" r="F12" s="106">
+        <f>D12+E12</f>
+        <v>5650.1</v>
+      </c>
+      <c t="n" r="G12" s="107">
+        <f>IFERROR(F12/C12,"")</f>
+        <v>0.225372955723973</v>
+      </c>
+      <c t="n" r="H12" s="106">
+        <f>IF(C12="","",C12-F12)</f>
+        <v>19419.9</v>
+      </c>
+      <c t="n" r="I12" s="106">
+        <f>IFERROR((F12/$B$7)*$B$6,"")</f>
+        <v>12430.22</v>
+      </c>
+      <c t="n" r="J12" s="107">
+        <f>IFERROR(I12/C12,"")</f>
+        <v>0.49582050259274</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="104" t="inlineStr">
+        <is>
+          <t>סופרפארם</t>
+        </is>
+      </c>
+      <c r="C13" s="105" t="n">
+        <v>167860</v>
+      </c>
+      <c r="D13" s="105" t="n">
+        <v>78350.3</v>
+      </c>
+      <c r="E13" s="108" t="n"/>
+      <c t="n" r="F13" s="106">
+        <f>D13+E13</f>
+        <v>78350.3</v>
+      </c>
+      <c t="n" r="G13" s="107">
+        <f>IFERROR(F13/C13,"")</f>
+        <v>0.466759799833194</v>
+      </c>
+      <c t="n" r="H13" s="106">
+        <f>IF(C13="","",C13-F13)</f>
+        <v>89509.7</v>
+      </c>
+      <c t="n" r="I13" s="106">
+        <f>IFERROR((F13/$B$7)*$B$6,"")</f>
+        <v>172370.66</v>
+      </c>
+      <c t="n" r="J13" s="107">
+        <f>IFERROR(I13/C13,"")</f>
+        <v>1.02687155963303</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="109" t="n"/>
+      <c r="B14" s="110" t="inlineStr">
+        <is>
+          <t>סה"כ</t>
+        </is>
+      </c>
+      <c t="n" r="C14" s="111">
+        <f>SUM(C11:C13)</f>
+        <v>238710</v>
+      </c>
+      <c t="n" r="D14" s="111">
+        <f>SUM(D11:D13)</f>
+        <v>112199.3</v>
+      </c>
+      <c t="n" r="E14" s="111">
+        <f>SUM(E11:E13)</f>
+        <v>1205</v>
+      </c>
+      <c t="n" r="F14" s="111">
+        <f>SUM(F11:F13)</f>
+        <v>113404.3</v>
+      </c>
+      <c t="n" r="G14" s="112">
+        <f>IFERROR(F14/C14,"")</f>
+        <v>0.475071425579155</v>
+      </c>
+      <c t="n" r="H14" s="111">
+        <f>IF(C14="","",C14-F14)</f>
+        <v>125305.7</v>
+      </c>
+      <c t="n" r="I14" s="111">
+        <f>IFERROR((F14/$B$7)*$B$6,"")</f>
+        <v>249489.46</v>
+      </c>
+      <c t="n" r="J14" s="112">
+        <f>IFERROR(I14/C14,"")</f>
+        <v>1.04515713627414</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="104" t="inlineStr">
+        <is>
+          <t>מכוני אורטופדיה</t>
+        </is>
+      </c>
+      <c r="C15" s="105" t="n">
+        <v>28992</v>
+      </c>
+      <c r="D15" s="105" t="n">
+        <v>8622</v>
+      </c>
+      <c r="E15" s="108" t="n"/>
+      <c t="n" r="F15" s="106">
+        <f>D15+E15</f>
+        <v>8622</v>
+      </c>
+      <c t="n" r="G15" s="107">
+        <f>IFERROR(F15/C15,"")</f>
+        <v>0.29739238410596</v>
+      </c>
+      <c t="n" r="H15" s="106">
+        <f>IF(C15="","",C15-F15)</f>
+        <v>20370</v>
+      </c>
+      <c t="n" r="I15" s="106">
+        <f>IFERROR((F15/$B$7)*$B$6,"")</f>
+        <v>18968.4</v>
+      </c>
+      <c t="n" r="J15" s="107">
+        <f>IFERROR(I15/C15,"")</f>
+        <v>0.654263245033113</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="104" t="inlineStr">
+        <is>
+          <t>מכוני פיזוטרפיה</t>
+        </is>
+      </c>
+      <c r="C16" s="113" t="n"/>
+      <c r="D16" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="108" t="n"/>
+      <c t="n" r="F16" s="106">
+        <f>D16+E16</f>
+        <v>0</v>
+      </c>
+      <c t="str" r="G16" s="107">
+        <f>IFERROR(F16/C16,"")</f>
+        <v/>
+      </c>
+      <c t="str" r="H16" s="106">
+        <f>IF(C16="","",C16-F16)</f>
+        <v/>
+      </c>
+      <c t="n" r="I16" s="106">
+        <f>IFERROR((F16/$B$7)*$B$6,"")</f>
+        <v>0</v>
+      </c>
+      <c t="str" r="J16" s="107">
+        <f>IFERROR(I16/C16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="104" t="inlineStr">
+        <is>
+          <t>מאוחדת</t>
+        </is>
+      </c>
+      <c r="C17" s="105" t="n">
+        <v>43600</v>
+      </c>
+      <c r="D17" s="105" t="n">
+        <v>27849.1</v>
+      </c>
+      <c r="E17" s="105" t="n">
+        <v>2240</v>
+      </c>
+      <c t="n" r="F17" s="106">
+        <f>D17+E17</f>
+        <v>30089.1</v>
+      </c>
+      <c t="n" r="G17" s="107">
+        <f>IFERROR(F17/C17,"")</f>
+        <v>0.690116972477064</v>
+      </c>
+      <c t="n" r="H17" s="106">
+        <f>IF(C17="","",C17-F17)</f>
+        <v>13510.9</v>
+      </c>
+      <c t="n" r="I17" s="106">
+        <f>IFERROR((F17/$B$7)*$B$6,"")</f>
+        <v>66196.02</v>
+      </c>
+      <c t="n" r="J17" s="107">
+        <f>IFERROR(I17/C17,"")</f>
+        <v>1.51825733944954</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="104" t="inlineStr">
+        <is>
+          <t>חנויות פרטיות</t>
+        </is>
+      </c>
+      <c r="C18" s="105" t="n">
+        <v>6250</v>
+      </c>
+      <c r="D18" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="108" t="n"/>
+      <c t="n" r="F18" s="106">
+        <f>D18+E18</f>
+        <v>0</v>
+      </c>
+      <c t="n" r="G18" s="107">
+        <f>IFERROR(F18/C18,"")</f>
+        <v>0</v>
+      </c>
+      <c t="n" r="H18" s="106">
+        <f>IF(C18="","",C18-F18)</f>
+        <v>6250</v>
+      </c>
+      <c t="n" r="I18" s="106">
+        <f>IFERROR((F18/$B$7)*$B$6,"")</f>
+        <v>0</v>
+      </c>
+      <c t="n" r="J18" s="107">
+        <f>IFERROR(I18/C18,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="104" t="inlineStr">
+        <is>
+          <t>חנויות ספורט</t>
+        </is>
+      </c>
+      <c r="C19" s="113" t="n"/>
+      <c r="D19" s="105" t="n">
+        <v>457</v>
+      </c>
+      <c r="E19" s="108" t="n"/>
+      <c t="n" r="F19" s="106">
+        <f>D19+E19</f>
+        <v>457</v>
+      </c>
+      <c t="str" r="G19" s="107">
+        <f>IFERROR(F19/C19,"")</f>
+        <v/>
+      </c>
+      <c t="str" r="H19" s="106">
+        <f>IF(C19="","",C19-F19)</f>
+        <v/>
+      </c>
+      <c t="n" r="I19" s="106">
+        <f>IFERROR((F19/$B$7)*$B$6,"")</f>
+        <v>1005.4</v>
+      </c>
+      <c t="str" r="J19" s="107">
+        <f>IFERROR(I19/C19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="114" t="n"/>
+      <c r="B20" s="110" t="inlineStr">
+        <is>
+          <t>סה"כ</t>
+        </is>
+      </c>
+      <c t="n" r="C20" s="111">
+        <f>SUM(C15:C19)</f>
+        <v>78842</v>
+      </c>
+      <c t="n" r="D20" s="111">
+        <f>SUM(D15:D19)</f>
+        <v>36928.1</v>
+      </c>
+      <c t="n" r="E20" s="111">
+        <f>SUM(E15:E19)</f>
+        <v>2240</v>
+      </c>
+      <c t="n" r="F20" s="111">
+        <f>SUM(F15:F19)</f>
+        <v>39168.1</v>
+      </c>
+      <c t="n" r="G20" s="112">
+        <f>IFERROR(F20/C20,"")</f>
+        <v>0.496792318814845</v>
+      </c>
+      <c t="n" r="H20" s="111">
+        <f>IF(C20="","",C20-F20)</f>
+        <v>39673.9</v>
+      </c>
+      <c t="n" r="I20" s="111">
+        <f>IFERROR((F20/$B$7)*$B$6,"")</f>
+        <v>86169.82</v>
+      </c>
+      <c t="n" r="J20" s="112">
+        <f>IFERROR(I20/C20,"")</f>
+        <v>1.09294310139266</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="115" t="n"/>
+      <c r="B21" s="116" t="inlineStr">
+        <is>
+          <t>סה"כ כללי</t>
+        </is>
+      </c>
+      <c t="n" r="C21" s="117">
+        <f>C14+C20</f>
+        <v>317552</v>
+      </c>
+      <c t="n" r="D21" s="117">
+        <f>D14+D20</f>
+        <v>149127.4</v>
+      </c>
+      <c t="n" r="E21" s="117">
+        <f>E14+E20</f>
+        <v>3445</v>
+      </c>
+      <c t="n" r="F21" s="117">
+        <f>F14+F20</f>
+        <v>152572.4</v>
+      </c>
+      <c t="n" r="G21" s="118">
+        <f>IFERROR(F21/C21,"")</f>
+        <v>0.480464301909609</v>
+      </c>
+      <c t="n" r="H21" s="117">
+        <f>IF(C21="","",C21-F21)</f>
+        <v>164979.6</v>
+      </c>
+      <c t="n" r="I21" s="117">
+        <f>IFERROR((F21/$B$7)*$B$6,"")</f>
+        <v>335659.28</v>
+      </c>
+      <c t="n" r="J21" s="118">
+        <f>IFERROR(I21/C21,"")</f>
+        <v>1.05702146420114</v>
+      </c>
+    </row>
+    <row r="23" ht="19.5" customHeight="1" s="49">
+      <c r="A23" s="71" t="inlineStr">
+        <is>
+          <t>סיכום ביצועים — סה"כ כללי (דודו)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="8" customHeight="1" s="49"/>
+    <row r="25" ht="30" customHeight="1" s="49">
+      <c r="A25" s="72" t="inlineStr">
+        <is>
+          <t>ימים שנותרו (א'-ה', עד סוף החודש)</t>
+        </is>
+      </c>
+      <c r="D25" s="72" t="inlineStr">
+        <is>
+          <t>יעד יומי נדרש להשלמה (₪)</t>
+        </is>
+      </c>
+      <c r="G25" s="72" t="inlineStr">
+        <is>
+          <t>אחוז ביצוע נוכחי (מתוך היעד הכולל)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1" s="49">
+      <c t="n" r="A26" s="73">
+        <f>IFERROR(B6-B7,"—")</f>
+        <v>12</v>
+      </c>
+      <c t="n" r="D26" s="119">
+        <f>IFERROR(H21/(B6-B7),"—")</f>
+        <v>13748.3</v>
+      </c>
+      <c t="n" r="G26" s="75">
+        <f>IFERROR((D21+E21)/C21,"—")</f>
+        <v>0.480464301909609</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" s="49">
+      <c r="A28" s="76" t="inlineStr">
+        <is>
+          <t>הערה: "ימים שנותרו" = סה"כ ימי א'-ה' בחודש (B6) פחות ימי א'-ה' שעברו עד יום הבדיקה (B7). "יעד יומי נדרש" = הסכום שנותר להשלמת היעד הכללי (H21) חלקי הימים שנותרו. עיצוב מותנה על תא האחוז: אדום מתחת ל-33%, צהוב 33%-66%, ירוק מעל 66%.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A25:C25"/>
@@ -3206,14 +3993,1277 @@
       <formula>0.66</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <legacyDrawing ns1:id="anysvml"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="49" min="1" max="1"/>
+    <col width="22" customWidth="1" style="49" min="2" max="2"/>
+    <col width="13" customWidth="1" style="49" min="3" max="3"/>
+    <col width="15" customWidth="1" style="49" min="4" max="4"/>
+    <col width="13" customWidth="1" style="49" min="5" max="5"/>
+    <col width="16" customWidth="1" style="49" min="6" max="6"/>
+    <col width="13" customWidth="1" style="49" min="7" max="7"/>
+    <col width="16" customWidth="1" style="49" min="8" max="8"/>
+    <col width="16" customWidth="1" style="49" min="9" max="9"/>
+    <col width="10" customWidth="1" style="49" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="95" t="inlineStr">
+        <is>
+          <t>מעקב ביצועי סוכן חיים</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="96" t="inlineStr">
+        <is>
+          <t>תאריך חישוב:</t>
+        </is>
+      </c>
+      <c r="B2" s="97" t="n">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="96" t="inlineStr">
+        <is>
+          <t>יום בדיקה (קלט ידני):</t>
+        </is>
+      </c>
+      <c r="B3" s="98" t="n">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="96" t="inlineStr">
+        <is>
+          <t>תחילת החודש הרלוונטי:</t>
+        </is>
+      </c>
+      <c t="n" r="B4" s="97">
+        <f>EOMONTH(B3,-1)+1</f>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="96" t="inlineStr">
+        <is>
+          <t>סוף החודש הרלוונטי:</t>
+        </is>
+      </c>
+      <c t="n" r="B5" s="97">
+        <f>EOMONTH(B3,0)</f>
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="96" t="inlineStr">
+        <is>
+          <t>סה"כ ימי א'-ה' בחודש:</t>
+        </is>
+      </c>
+      <c t="n" r="B6" s="99">
+        <f>SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B5)))&lt;6)*1)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="96" t="inlineStr">
+        <is>
+          <t>ימי א'-ה' שעברו (מ-1 בחודש עד יום הבדיקה):</t>
+        </is>
+      </c>
+      <c t="n" r="B7" s="99">
+        <f>SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B3)))&lt;6)*1)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1" s="49">
+      <c r="A8" s="100" t="inlineStr">
+        <is>
+          <t>הערה: עמודות D ('מכירות') ו-E ('פתוחות') הן צילום מצב (snapshot) של הערכים המחושבים (קאש) שכבר קיימים בקובץ המקור שהועלה (agents-tracking-source-full.xlsx, גיליון 'חיים'), שם הם תוצאה של נוסחאות פנימיות מול גיליונות 'מכירות'/'פתוחות' באותו קובץ. הועתקו לכאן כערכים קשיחים (לא לינק חי), בהתאם לאותה שיטה שבה נבנה גיליון חאזם. לתשומת לב - פער בנתוני המקור: לא נמצא יעד חודשי (עמודה C) לקטגוריות: חנויות ספורט. עד להשלמה ידנית, אחוז ביצוע וקצב % לקטגוריות אלה יוצגו כריק.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" s="49">
+      <c r="A9" s="101" t="inlineStr">
+        <is>
+          <t>גיליון זה = נתוני מקור וחישוב (Working Data): כל הנוסחאות, המקור וה-snapshot המלאים נמצאים כאן. לתצוגת סיכום ויזואלית עם גרפים למנהל  ⇦  עבור לגיליון DASHBOARD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="31.5" customHeight="1" s="49">
+      <c r="A10" s="102" t="inlineStr">
+        <is>
+          <t>סוכן</t>
+        </is>
+      </c>
+      <c r="B10" s="102" t="inlineStr">
+        <is>
+          <t>קטגוריה</t>
+        </is>
+      </c>
+      <c r="C10" s="102" t="inlineStr">
+        <is>
+          <t>יעד חודשי (₪)</t>
+        </is>
+      </c>
+      <c r="D10" s="102" t="inlineStr">
+        <is>
+          <t>מכירות (snapshot)</t>
+        </is>
+      </c>
+      <c r="E10" s="102" t="inlineStr">
+        <is>
+          <t>פתוחות (snapshot)</t>
+        </is>
+      </c>
+      <c r="F10" s="102" t="inlineStr">
+        <is>
+          <t>מכירות עד לבדיקה (₪)</t>
+        </is>
+      </c>
+      <c r="G10" s="102" t="inlineStr">
+        <is>
+          <t>אחוז ביצוע לפי יעד</t>
+        </is>
+      </c>
+      <c r="H10" s="102" t="inlineStr">
+        <is>
+          <t>כמה נשאר לסיום החודש (₪)</t>
+        </is>
+      </c>
+      <c r="I10" s="102" t="inlineStr">
+        <is>
+          <t>קצב אומדן סוף חודש (₪)</t>
+        </is>
+      </c>
+      <c r="J10" s="102" t="inlineStr">
+        <is>
+          <t>קצב %</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="103" t="inlineStr">
+        <is>
+          <t>חיים</t>
+        </is>
+      </c>
+      <c r="B11" s="104" t="inlineStr">
+        <is>
+          <t>בתי מרקחת פרטיים</t>
+        </is>
+      </c>
+      <c r="C11" s="105" t="n">
+        <v>30520</v>
+      </c>
+      <c r="D11" s="105" t="n">
+        <v>13592.7</v>
+      </c>
+      <c r="E11" s="105" t="n">
+        <v>75</v>
+      </c>
+      <c t="n" r="F11" s="106">
+        <f>D11+E11</f>
+        <v>13667.7</v>
+      </c>
+      <c t="n" r="G11" s="107">
+        <f>IFERROR(F11/C11,"")</f>
+        <v>0.447827653997379</v>
+      </c>
+      <c t="n" r="H11" s="106">
+        <f>IF(C11="","",C11-F11)</f>
+        <v>16852.3</v>
+      </c>
+      <c t="n" r="I11" s="106">
+        <f>IFERROR((F11/$B$7)*$B$6,"")</f>
+        <v>30068.94</v>
+      </c>
+      <c t="n" r="J11" s="107">
+        <f>IFERROR(I11/C11,"")</f>
+        <v>0.985220838794233</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="104" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C12" s="105" t="n">
+        <v>30520</v>
+      </c>
+      <c r="D12" s="105" t="n">
+        <v>9861.200000000001</v>
+      </c>
+      <c r="E12" s="105" t="n">
+        <v>408</v>
+      </c>
+      <c t="n" r="F12" s="106">
+        <f>D12+E12</f>
+        <v>10269.2</v>
+      </c>
+      <c t="n" r="G12" s="107">
+        <f>IFERROR(F12/C12,"")</f>
+        <v>0.336474442988205</v>
+      </c>
+      <c t="n" r="H12" s="106">
+        <f>IF(C12="","",C12-F12)</f>
+        <v>20250.8</v>
+      </c>
+      <c t="n" r="I12" s="106">
+        <f>IFERROR((F12/$B$7)*$B$6,"")</f>
+        <v>22592.24</v>
+      </c>
+      <c t="n" r="J12" s="107">
+        <f>IFERROR(I12/C12,"")</f>
+        <v>0.74024377457405</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="104" t="inlineStr">
+        <is>
+          <t>סופרפארם</t>
+        </is>
+      </c>
+      <c r="C13" s="105" t="n">
+        <v>161865</v>
+      </c>
+      <c r="D13" s="105" t="n">
+        <v>64049.2</v>
+      </c>
+      <c r="E13" s="108" t="n"/>
+      <c t="n" r="F13" s="106">
+        <f>D13+E13</f>
+        <v>64049.2</v>
+      </c>
+      <c t="n" r="G13" s="107">
+        <f>IFERROR(F13/C13,"")</f>
+        <v>0.395695178080499</v>
+      </c>
+      <c t="n" r="H13" s="106">
+        <f>IF(C13="","",C13-F13)</f>
+        <v>97815.8</v>
+      </c>
+      <c t="n" r="I13" s="106">
+        <f>IFERROR((F13/$B$7)*$B$6,"")</f>
+        <v>140908.24</v>
+      </c>
+      <c t="n" r="J13" s="107">
+        <f>IFERROR(I13/C13,"")</f>
+        <v>0.870529391777098</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="109" t="n"/>
+      <c r="B14" s="110" t="inlineStr">
+        <is>
+          <t>סה"כ</t>
+        </is>
+      </c>
+      <c t="n" r="C14" s="111">
+        <f>SUM(C11:C13)</f>
+        <v>222905</v>
+      </c>
+      <c t="n" r="D14" s="111">
+        <f>SUM(D11:D13)</f>
+        <v>87503.1</v>
+      </c>
+      <c t="n" r="E14" s="111">
+        <f>SUM(E11:E13)</f>
+        <v>483</v>
+      </c>
+      <c t="n" r="F14" s="111">
+        <f>SUM(F11:F13)</f>
+        <v>87986.1</v>
+      </c>
+      <c t="n" r="G14" s="112">
+        <f>IFERROR(F14/C14,"")</f>
+        <v>0.394724658486799</v>
+      </c>
+      <c t="n" r="H14" s="111">
+        <f>IF(C14="","",C14-F14)</f>
+        <v>134918.9</v>
+      </c>
+      <c t="n" r="I14" s="111">
+        <f>IFERROR((F14/$B$7)*$B$6,"")</f>
+        <v>193569.42</v>
+      </c>
+      <c t="n" r="J14" s="112">
+        <f>IFERROR(I14/C14,"")</f>
+        <v>0.868394248670959</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="104" t="inlineStr">
+        <is>
+          <t>מכוני אורטופדיה</t>
+        </is>
+      </c>
+      <c r="C15" s="105" t="n">
+        <v>12794</v>
+      </c>
+      <c r="D15" s="105" t="n">
+        <v>4269</v>
+      </c>
+      <c r="E15" s="108" t="n"/>
+      <c t="n" r="F15" s="106">
+        <f>D15+E15</f>
+        <v>4269</v>
+      </c>
+      <c t="n" r="G15" s="107">
+        <f>IFERROR(F15/C15,"")</f>
+        <v>0.333672033765828</v>
+      </c>
+      <c t="n" r="H15" s="106">
+        <f>IF(C15="","",C15-F15)</f>
+        <v>8525</v>
+      </c>
+      <c t="n" r="I15" s="106">
+        <f>IFERROR((F15/$B$7)*$B$6,"")</f>
+        <v>9391.8</v>
+      </c>
+      <c t="n" r="J15" s="107">
+        <f>IFERROR(I15/C15,"")</f>
+        <v>0.734078474284821</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="104" t="inlineStr">
+        <is>
+          <t>מכוני פיזוטרפיה</t>
+        </is>
+      </c>
+      <c r="C16" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="108" t="n"/>
+      <c t="n" r="F16" s="106">
+        <f>D16+E16</f>
+        <v>0</v>
+      </c>
+      <c t="str" r="G16" s="107">
+        <f>IFERROR(F16/C16,"")</f>
+        <v/>
+      </c>
+      <c t="n" r="H16" s="106">
+        <f>IF(C16="","",C16-F16)</f>
+        <v>0</v>
+      </c>
+      <c t="n" r="I16" s="106">
+        <f>IFERROR((F16/$B$7)*$B$6,"")</f>
+        <v>0</v>
+      </c>
+      <c t="str" r="J16" s="107">
+        <f>IFERROR(I16/C16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="104" t="inlineStr">
+        <is>
+          <t>מאוחדת</t>
+        </is>
+      </c>
+      <c r="C17" s="105" t="n">
+        <v>6625</v>
+      </c>
+      <c r="D17" s="105" t="n">
+        <v>4045</v>
+      </c>
+      <c r="E17" s="105" t="n">
+        <v>537</v>
+      </c>
+      <c t="n" r="F17" s="106">
+        <f>D17+E17</f>
+        <v>4582</v>
+      </c>
+      <c t="n" r="G17" s="107">
+        <f>IFERROR(F17/C17,"")</f>
+        <v>0.691622641509434</v>
+      </c>
+      <c t="n" r="H17" s="106">
+        <f>IF(C17="","",C17-F17)</f>
+        <v>2043</v>
+      </c>
+      <c t="n" r="I17" s="106">
+        <f>IFERROR((F17/$B$7)*$B$6,"")</f>
+        <v>10080.4</v>
+      </c>
+      <c t="n" r="J17" s="107">
+        <f>IFERROR(I17/C17,"")</f>
+        <v>1.52156981132075</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="104" t="inlineStr">
+        <is>
+          <t>חנויות פרטיות</t>
+        </is>
+      </c>
+      <c r="C18" s="105" t="n">
+        <v>22036</v>
+      </c>
+      <c r="D18" s="105" t="n">
+        <v>1212</v>
+      </c>
+      <c r="E18" s="108" t="n"/>
+      <c t="n" r="F18" s="106">
+        <f>D18+E18</f>
+        <v>1212</v>
+      </c>
+      <c t="n" r="G18" s="107">
+        <f>IFERROR(F18/C18,"")</f>
+        <v>0.0550009076057361</v>
+      </c>
+      <c t="n" r="H18" s="106">
+        <f>IF(C18="","",C18-F18)</f>
+        <v>20824</v>
+      </c>
+      <c t="n" r="I18" s="106">
+        <f>IFERROR((F18/$B$7)*$B$6,"")</f>
+        <v>2666.4</v>
+      </c>
+      <c t="n" r="J18" s="107">
+        <f>IFERROR(I18/C18,"")</f>
+        <v>0.121001996732619</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="104" t="inlineStr">
+        <is>
+          <t>חנויות ספורט</t>
+        </is>
+      </c>
+      <c r="C19" s="113" t="n"/>
+      <c r="D19" s="105" t="n"/>
+      <c r="E19" s="108" t="n"/>
+      <c t="n" r="F19" s="106">
+        <f>D19+E19</f>
+        <v>0</v>
+      </c>
+      <c t="str" r="G19" s="107">
+        <f>IFERROR(F19/C19,"")</f>
+        <v/>
+      </c>
+      <c t="str" r="H19" s="106">
+        <f>IF(C19="","",C19-F19)</f>
+        <v/>
+      </c>
+      <c t="n" r="I19" s="106">
+        <f>IFERROR((F19/$B$7)*$B$6,"")</f>
+        <v>0</v>
+      </c>
+      <c t="str" r="J19" s="107">
+        <f>IFERROR(I19/C19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="114" t="n"/>
+      <c r="B20" s="110" t="inlineStr">
+        <is>
+          <t>סה"כ</t>
+        </is>
+      </c>
+      <c t="n" r="C20" s="111">
+        <f>SUM(C15:C19)</f>
+        <v>41455</v>
+      </c>
+      <c t="n" r="D20" s="111">
+        <f>SUM(D15:D19)</f>
+        <v>9526</v>
+      </c>
+      <c t="n" r="E20" s="111">
+        <f>SUM(E15:E19)</f>
+        <v>537</v>
+      </c>
+      <c t="n" r="F20" s="111">
+        <f>SUM(F15:F19)</f>
+        <v>10063</v>
+      </c>
+      <c t="n" r="G20" s="112">
+        <f>IFERROR(F20/C20,"")</f>
+        <v>0.242745145338319</v>
+      </c>
+      <c t="n" r="H20" s="111">
+        <f>IF(C20="","",C20-F20)</f>
+        <v>31392</v>
+      </c>
+      <c t="n" r="I20" s="111">
+        <f>IFERROR((F20/$B$7)*$B$6,"")</f>
+        <v>22138.6</v>
+      </c>
+      <c t="n" r="J20" s="112">
+        <f>IFERROR(I20/C20,"")</f>
+        <v>0.534039319744301</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="115" t="n"/>
+      <c r="B21" s="116" t="inlineStr">
+        <is>
+          <t>סה"כ כללי</t>
+        </is>
+      </c>
+      <c t="n" r="C21" s="117">
+        <f>C14+C20</f>
+        <v>264360</v>
+      </c>
+      <c t="n" r="D21" s="117">
+        <f>D14+D20</f>
+        <v>97029.1</v>
+      </c>
+      <c t="n" r="E21" s="117">
+        <f>E14+E20</f>
+        <v>1020</v>
+      </c>
+      <c t="n" r="F21" s="117">
+        <f>F14+F20</f>
+        <v>98049.1</v>
+      </c>
+      <c t="n" r="G21" s="118">
+        <f>IFERROR(F21/C21,"")</f>
+        <v>0.370892343773642</v>
+      </c>
+      <c t="n" r="H21" s="117">
+        <f>IF(C21="","",C21-F21)</f>
+        <v>166310.9</v>
+      </c>
+      <c t="n" r="I21" s="117">
+        <f>IFERROR((F21/$B$7)*$B$6,"")</f>
+        <v>215708.02</v>
+      </c>
+      <c t="n" r="J21" s="118">
+        <f>IFERROR(I21/C21,"")</f>
+        <v>0.815963156302012</v>
+      </c>
+    </row>
+    <row r="23" ht="19.5" customHeight="1" s="49">
+      <c r="A23" s="71" t="inlineStr">
+        <is>
+          <t>סיכום ביצועים — סה"כ כללי (חיים)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="8" customHeight="1" s="49"/>
+    <row r="25" ht="30" customHeight="1" s="49">
+      <c r="A25" s="72" t="inlineStr">
+        <is>
+          <t>ימים שנותרו (א'-ה', עד סוף החודש)</t>
+        </is>
+      </c>
+      <c r="D25" s="72" t="inlineStr">
+        <is>
+          <t>יעד יומי נדרש להשלמה (₪)</t>
+        </is>
+      </c>
+      <c r="G25" s="72" t="inlineStr">
+        <is>
+          <t>אחוז ביצוע נוכחי (מתוך היעד הכולל)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1" s="49">
+      <c t="n" r="A26" s="73">
+        <f>IFERROR(B6-B7,"—")</f>
+        <v>12</v>
+      </c>
+      <c t="n" r="D26" s="119">
+        <f>IFERROR(H21/(B6-B7),"—")</f>
+        <v>13859.2416666667</v>
+      </c>
+      <c t="n" r="G26" s="75">
+        <f>IFERROR((D21+E21)/C21,"—")</f>
+        <v>0.370892343773642</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" s="49">
+      <c r="A28" s="76" t="inlineStr">
+        <is>
+          <t>הערה: "ימים שנותרו" = סה"כ ימי א'-ה' בחודש (B6) פחות ימי א'-ה' שעברו עד יום הבדיקה (B7). "יעד יומי נדרש" = הסכום שנותר להשלמת היעד הכללי (H21) חלקי הימים שנותרו. עיצוב מותנה על תא האחוז: אדום מתחת ל-33%, צהוב 33%-66%, ירוק מעל 66%.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="A11:A19"/>
+    <mergeCell ref="A26:C26"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="2">
+      <formula>0.33</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="3">
+      <formula>0.66</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="4">
+      <formula>0.66</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="49" min="1" max="1"/>
+    <col width="22" customWidth="1" style="49" min="2" max="2"/>
+    <col width="13" customWidth="1" style="49" min="3" max="3"/>
+    <col width="15" customWidth="1" style="49" min="4" max="4"/>
+    <col width="13" customWidth="1" style="49" min="5" max="5"/>
+    <col width="16" customWidth="1" style="49" min="6" max="6"/>
+    <col width="13" customWidth="1" style="49" min="7" max="7"/>
+    <col width="16" customWidth="1" style="49" min="8" max="8"/>
+    <col width="16" customWidth="1" style="49" min="9" max="9"/>
+    <col width="10" customWidth="1" style="49" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="95" t="inlineStr">
+        <is>
+          <t>מעקב ביצועי סוכן סטאס</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="96" t="inlineStr">
+        <is>
+          <t>תאריך חישוב:</t>
+        </is>
+      </c>
+      <c r="B2" s="97" t="n">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="96" t="inlineStr">
+        <is>
+          <t>יום בדיקה (קלט ידני):</t>
+        </is>
+      </c>
+      <c r="B3" s="98" t="n">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="96" t="inlineStr">
+        <is>
+          <t>תחילת החודש הרלוונטי:</t>
+        </is>
+      </c>
+      <c t="n" r="B4" s="97">
+        <f>EOMONTH(B3,-1)+1</f>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="96" t="inlineStr">
+        <is>
+          <t>סוף החודש הרלוונטי:</t>
+        </is>
+      </c>
+      <c t="n" r="B5" s="97">
+        <f>EOMONTH(B3,0)</f>
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="96" t="inlineStr">
+        <is>
+          <t>סה"כ ימי א'-ה' בחודש:</t>
+        </is>
+      </c>
+      <c t="n" r="B6" s="99">
+        <f>SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B5)))&lt;6)*1)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="96" t="inlineStr">
+        <is>
+          <t>ימי א'-ה' שעברו (מ-1 בחודש עד יום הבדיקה):</t>
+        </is>
+      </c>
+      <c t="n" r="B7" s="99">
+        <f>SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B3)))&lt;6)*1)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1" s="49">
+      <c r="A8" s="100" t="inlineStr">
+        <is>
+          <t>הערה: עמודות D ('מכירות') ו-E ('פתוחות') הן צילום מצב (snapshot) של הערכים המחושבים (קאש) שכבר קיימים בקובץ המקור שהועלה (agents-tracking-source-full.xlsx, גיליון 'סטאס'), שם הם תוצאה של נוסחאות פנימיות מול גיליונות 'מכירות'/'פתוחות' באותו קובץ. הועתקו לכאן כערכים קשיחים (לא לינק חי), בהתאם לאותה שיטה שבה נבנה גיליון חאזם. לתשומת לב - פער בנתוני המקור: לא נמצא יעד חודשי (עמודה C) לקטגוריות: חנויות ספורט. עד להשלמה ידנית, אחוז ביצוע וקצב % לקטגוריות אלה יוצגו כריק.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" s="49">
+      <c r="A9" s="101" t="inlineStr">
+        <is>
+          <t>גיליון זה = נתוני מקור וחישוב (Working Data): כל הנוסחאות, המקור וה-snapshot המלאים נמצאים כאן. לתצוגת סיכום ויזואלית עם גרפים למנהל  ⇦  עבור לגיליון DASHBOARD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="31.5" customHeight="1" s="49">
+      <c r="A10" s="102" t="inlineStr">
+        <is>
+          <t>סוכן</t>
+        </is>
+      </c>
+      <c r="B10" s="102" t="inlineStr">
+        <is>
+          <t>קטגוריה</t>
+        </is>
+      </c>
+      <c r="C10" s="102" t="inlineStr">
+        <is>
+          <t>יעד חודשי (₪)</t>
+        </is>
+      </c>
+      <c r="D10" s="102" t="inlineStr">
+        <is>
+          <t>מכירות (snapshot)</t>
+        </is>
+      </c>
+      <c r="E10" s="102" t="inlineStr">
+        <is>
+          <t>פתוחות (snapshot)</t>
+        </is>
+      </c>
+      <c r="F10" s="102" t="inlineStr">
+        <is>
+          <t>מכירות עד לבדיקה (₪)</t>
+        </is>
+      </c>
+      <c r="G10" s="102" t="inlineStr">
+        <is>
+          <t>אחוז ביצוע לפי יעד</t>
+        </is>
+      </c>
+      <c r="H10" s="102" t="inlineStr">
+        <is>
+          <t>כמה נשאר לסיום החודש (₪)</t>
+        </is>
+      </c>
+      <c r="I10" s="102" t="inlineStr">
+        <is>
+          <t>קצב אומדן סוף חודש (₪)</t>
+        </is>
+      </c>
+      <c r="J10" s="102" t="inlineStr">
+        <is>
+          <t>קצב %</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="103" t="inlineStr">
+        <is>
+          <t>סטאס</t>
+        </is>
+      </c>
+      <c r="B11" s="104" t="inlineStr">
+        <is>
+          <t>בתי מרקחת פרטיים</t>
+        </is>
+      </c>
+      <c r="C11" s="105" t="n">
+        <v>32700</v>
+      </c>
+      <c r="D11" s="105" t="n">
+        <v>10036.8</v>
+      </c>
+      <c r="E11" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c t="n" r="F11" s="106">
+        <f>D11+E11</f>
+        <v>10036.8</v>
+      </c>
+      <c t="n" r="G11" s="107">
+        <f>IFERROR(F11/C11,"")</f>
+        <v>0.306935779816514</v>
+      </c>
+      <c t="n" r="H11" s="106">
+        <f>IF(C11="","",C11-F11)</f>
+        <v>22663.2</v>
+      </c>
+      <c t="n" r="I11" s="106">
+        <f>IFERROR((F11/$B$7)*$B$6,"")</f>
+        <v>22080.96</v>
+      </c>
+      <c t="n" r="J11" s="107">
+        <f>IFERROR(I11/C11,"")</f>
+        <v>0.67525871559633</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="104" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C12" s="105" t="n">
+        <v>28340</v>
+      </c>
+      <c r="D12" s="105" t="n">
+        <v>11639.9</v>
+      </c>
+      <c r="E12" s="105" t="n">
+        <v>481</v>
+      </c>
+      <c t="n" r="F12" s="106">
+        <f>D12+E12</f>
+        <v>12120.9</v>
+      </c>
+      <c t="n" r="G12" s="107">
+        <f>IFERROR(F12/C12,"")</f>
+        <v>0.427695836273818</v>
+      </c>
+      <c t="n" r="H12" s="106">
+        <f>IF(C12="","",C12-F12)</f>
+        <v>16219.1</v>
+      </c>
+      <c t="n" r="I12" s="106">
+        <f>IFERROR((F12/$B$7)*$B$6,"")</f>
+        <v>26665.98</v>
+      </c>
+      <c t="n" r="J12" s="107">
+        <f>IFERROR(I12/C12,"")</f>
+        <v>0.940930839802399</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="104" t="inlineStr">
+        <is>
+          <t>סופרפארם</t>
+        </is>
+      </c>
+      <c r="C13" s="105" t="n">
+        <v>149875</v>
+      </c>
+      <c r="D13" s="105" t="n">
+        <v>56289.2</v>
+      </c>
+      <c r="E13" s="108" t="n"/>
+      <c t="n" r="F13" s="106">
+        <f>D13+E13</f>
+        <v>56289.2</v>
+      </c>
+      <c t="n" r="G13" s="107">
+        <f>IFERROR(F13/C13,"")</f>
+        <v>0.375574311926606</v>
+      </c>
+      <c t="n" r="H13" s="106">
+        <f>IF(C13="","",C13-F13)</f>
+        <v>93585.8</v>
+      </c>
+      <c t="n" r="I13" s="106">
+        <f>IFERROR((F13/$B$7)*$B$6,"")</f>
+        <v>123836.24</v>
+      </c>
+      <c t="n" r="J13" s="107">
+        <f>IFERROR(I13/C13,"")</f>
+        <v>0.826263486238532</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="109" t="n"/>
+      <c r="B14" s="110" t="inlineStr">
+        <is>
+          <t>סה"כ</t>
+        </is>
+      </c>
+      <c t="n" r="C14" s="111">
+        <f>SUM(C11:C13)</f>
+        <v>210915</v>
+      </c>
+      <c t="n" r="D14" s="111">
+        <f>SUM(D11:D13)</f>
+        <v>77965.9</v>
+      </c>
+      <c t="n" r="E14" s="111">
+        <f>SUM(E11:E13)</f>
+        <v>481</v>
+      </c>
+      <c t="n" r="F14" s="111">
+        <f>SUM(F11:F13)</f>
+        <v>78446.9</v>
+      </c>
+      <c t="n" r="G14" s="112">
+        <f>IFERROR(F14/C14,"")</f>
+        <v>0.371936087997535</v>
+      </c>
+      <c t="n" r="H14" s="111">
+        <f>IF(C14="","",C14-F14)</f>
+        <v>132468.1</v>
+      </c>
+      <c t="n" r="I14" s="111">
+        <f>IFERROR((F14/$B$7)*$B$6,"")</f>
+        <v>172583.18</v>
+      </c>
+      <c t="n" r="J14" s="112">
+        <f>IFERROR(I14/C14,"")</f>
+        <v>0.818259393594576</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="104" t="inlineStr">
+        <is>
+          <t>מכוני אורטופדיה</t>
+        </is>
+      </c>
+      <c r="C15" s="105" t="n">
+        <v>10756</v>
+      </c>
+      <c r="D15" s="105" t="n">
+        <v>1222</v>
+      </c>
+      <c r="E15" s="108" t="n"/>
+      <c t="n" r="F15" s="106">
+        <f>D15+E15</f>
+        <v>1222</v>
+      </c>
+      <c t="n" r="G15" s="107">
+        <f>IFERROR(F15/C15,"")</f>
+        <v>0.113611007809595</v>
+      </c>
+      <c t="n" r="H15" s="106">
+        <f>IF(C15="","",C15-F15)</f>
+        <v>9534</v>
+      </c>
+      <c t="n" r="I15" s="106">
+        <f>IFERROR((F15/$B$7)*$B$6,"")</f>
+        <v>2688.4</v>
+      </c>
+      <c t="n" r="J15" s="107">
+        <f>IFERROR(I15/C15,"")</f>
+        <v>0.249944217181108</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="104" t="inlineStr">
+        <is>
+          <t>מכוני פיזוטרפיה</t>
+        </is>
+      </c>
+      <c r="C16" s="105" t="n">
+        <v>7964</v>
+      </c>
+      <c r="D16" s="105" t="n">
+        <v>899</v>
+      </c>
+      <c r="E16" s="108" t="n"/>
+      <c t="n" r="F16" s="106">
+        <f>D16+E16</f>
+        <v>899</v>
+      </c>
+      <c t="n" r="G16" s="107">
+        <f>IFERROR(F16/C16,"")</f>
+        <v>0.112882973380211</v>
+      </c>
+      <c t="n" r="H16" s="106">
+        <f>IF(C16="","",C16-F16)</f>
+        <v>7065</v>
+      </c>
+      <c t="n" r="I16" s="106">
+        <f>IFERROR((F16/$B$7)*$B$6,"")</f>
+        <v>1977.8</v>
+      </c>
+      <c t="n" r="J16" s="107">
+        <f>IFERROR(I16/C16,"")</f>
+        <v>0.248342541436464</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="104" t="inlineStr">
+        <is>
+          <t>מאוחדת</t>
+        </is>
+      </c>
+      <c r="C17" s="105" t="n">
+        <v>21564</v>
+      </c>
+      <c r="D17" s="105" t="n">
+        <v>7584.6</v>
+      </c>
+      <c r="E17" s="105" t="n">
+        <v>132</v>
+      </c>
+      <c t="n" r="F17" s="106">
+        <f>D17+E17</f>
+        <v>7716.6</v>
+      </c>
+      <c t="n" r="G17" s="107">
+        <f>IFERROR(F17/C17,"")</f>
+        <v>0.357846410684474</v>
+      </c>
+      <c t="n" r="H17" s="106">
+        <f>IF(C17="","",C17-F17)</f>
+        <v>13847.4</v>
+      </c>
+      <c t="n" r="I17" s="106">
+        <f>IFERROR((F17/$B$7)*$B$6,"")</f>
+        <v>16976.52</v>
+      </c>
+      <c t="n" r="J17" s="107">
+        <f>IFERROR(I17/C17,"")</f>
+        <v>0.787262103505843</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="104" t="inlineStr">
+        <is>
+          <t>חנויות פרטיות</t>
+        </is>
+      </c>
+      <c r="C18" s="105" t="n">
+        <v>5875</v>
+      </c>
+      <c r="D18" s="105" t="n">
+        <v>157</v>
+      </c>
+      <c r="E18" s="108" t="n"/>
+      <c t="n" r="F18" s="106">
+        <f>D18+E18</f>
+        <v>157</v>
+      </c>
+      <c t="n" r="G18" s="107">
+        <f>IFERROR(F18/C18,"")</f>
+        <v>0.0267234042553192</v>
+      </c>
+      <c t="n" r="H18" s="106">
+        <f>IF(C18="","",C18-F18)</f>
+        <v>5718</v>
+      </c>
+      <c t="n" r="I18" s="106">
+        <f>IFERROR((F18/$B$7)*$B$6,"")</f>
+        <v>345.4</v>
+      </c>
+      <c t="n" r="J18" s="107">
+        <f>IFERROR(I18/C18,"")</f>
+        <v>0.0587914893617021</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="104" t="inlineStr">
+        <is>
+          <t>חנויות ספורט</t>
+        </is>
+      </c>
+      <c r="C19" s="113" t="n"/>
+      <c r="D19" s="105" t="n"/>
+      <c r="E19" s="108" t="n"/>
+      <c t="n" r="F19" s="106">
+        <f>D19+E19</f>
+        <v>0</v>
+      </c>
+      <c t="str" r="G19" s="107">
+        <f>IFERROR(F19/C19,"")</f>
+        <v/>
+      </c>
+      <c t="str" r="H19" s="106">
+        <f>IF(C19="","",C19-F19)</f>
+        <v/>
+      </c>
+      <c t="n" r="I19" s="106">
+        <f>IFERROR((F19/$B$7)*$B$6,"")</f>
+        <v>0</v>
+      </c>
+      <c t="str" r="J19" s="107">
+        <f>IFERROR(I19/C19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="114" t="n"/>
+      <c r="B20" s="110" t="inlineStr">
+        <is>
+          <t>סה"כ</t>
+        </is>
+      </c>
+      <c t="n" r="C20" s="111">
+        <f>SUM(C15:C19)</f>
+        <v>46159</v>
+      </c>
+      <c t="n" r="D20" s="111">
+        <f>SUM(D15:D19)</f>
+        <v>9862.6</v>
+      </c>
+      <c t="n" r="E20" s="111">
+        <f>SUM(E15:E19)</f>
+        <v>132</v>
+      </c>
+      <c t="n" r="F20" s="111">
+        <f>SUM(F15:F19)</f>
+        <v>9994.6</v>
+      </c>
+      <c t="n" r="G20" s="112">
+        <f>IFERROR(F20/C20,"")</f>
+        <v>0.216525487987175</v>
+      </c>
+      <c t="n" r="H20" s="111">
+        <f>IF(C20="","",C20-F20)</f>
+        <v>36164.4</v>
+      </c>
+      <c t="n" r="I20" s="111">
+        <f>IFERROR((F20/$B$7)*$B$6,"")</f>
+        <v>21988.12</v>
+      </c>
+      <c t="n" r="J20" s="112">
+        <f>IFERROR(I20/C20,"")</f>
+        <v>0.476356073571785</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="115" t="n"/>
+      <c r="B21" s="116" t="inlineStr">
+        <is>
+          <t>סה"כ כללי</t>
+        </is>
+      </c>
+      <c t="n" r="C21" s="117">
+        <f>C14+C20</f>
+        <v>257074</v>
+      </c>
+      <c t="n" r="D21" s="117">
+        <f>D14+D20</f>
+        <v>87828.5</v>
+      </c>
+      <c t="n" r="E21" s="117">
+        <f>E14+E20</f>
+        <v>613</v>
+      </c>
+      <c t="n" r="F21" s="117">
+        <f>F14+F20</f>
+        <v>88441.5</v>
+      </c>
+      <c t="n" r="G21" s="118">
+        <f>IFERROR(F21/C21,"")</f>
+        <v>0.34403129060115</v>
+      </c>
+      <c t="n" r="H21" s="117">
+        <f>IF(C21="","",C21-F21)</f>
+        <v>168632.5</v>
+      </c>
+      <c t="n" r="I21" s="117">
+        <f>IFERROR((F21/$B$7)*$B$6,"")</f>
+        <v>194571.3</v>
+      </c>
+      <c t="n" r="J21" s="118">
+        <f>IFERROR(I21/C21,"")</f>
+        <v>0.75686883932253</v>
+      </c>
+    </row>
+    <row r="23" ht="19.5" customHeight="1" s="49">
+      <c r="A23" s="71" t="inlineStr">
+        <is>
+          <t>סיכום ביצועים — סה"כ כללי (סטאס)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="8" customHeight="1" s="49"/>
+    <row r="25" ht="30" customHeight="1" s="49">
+      <c r="A25" s="72" t="inlineStr">
+        <is>
+          <t>ימים שנותרו (א'-ה', עד סוף החודש)</t>
+        </is>
+      </c>
+      <c r="D25" s="72" t="inlineStr">
+        <is>
+          <t>יעד יומי נדרש להשלמה (₪)</t>
+        </is>
+      </c>
+      <c r="G25" s="72" t="inlineStr">
+        <is>
+          <t>אחוז ביצוע נוכחי (מתוך היעד הכולל)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1" s="49">
+      <c t="n" r="A26" s="73">
+        <f>IFERROR(B6-B7,"—")</f>
+        <v>12</v>
+      </c>
+      <c t="n" r="D26" s="119">
+        <f>IFERROR(H21/(B6-B7),"—")</f>
+        <v>14052.7083333333</v>
+      </c>
+      <c t="n" r="G26" s="75">
+        <f>IFERROR((D21+E21)/C21,"—")</f>
+        <v>0.34403129060115</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" s="49">
+      <c r="A28" s="76" t="inlineStr">
+        <is>
+          <t>הערה: "ימים שנותרו" = סה"כ ימי א'-ה' בחודש (B6) פחות ימי א'-ה' שעברו עד יום הבדיקה (B7). "יעד יומי נדרש" = הסכום שנותר להשלמת היעד הכללי (H21) חלקי הימים שנותרו. עיצוב מותנה על תא האחוז: אדום מתחת ל-33%, צהוב 33%-66%, ירוק מעל 66%.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="A11:A19"/>
+    <mergeCell ref="A26:C26"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="2">
+      <formula>0.33</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="3">
+      <formula>0.66</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="4">
+      <formula>0.66</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FF548235"/>
@@ -3240,9 +5290,9 @@
       </c>
     </row>
     <row r="2" ht="21.75" customHeight="1" s="49">
-      <c r="A2" s="78">
+      <c t="str" r="A2" s="78">
         <f>"נכון לתאריך חישוב "&amp;TEXT(חאזם!B2,"dd/mm/yy")&amp;" | יום בדיקה: "&amp;TEXT(חאזם!B3,"dd/mm/yy")&amp;"  |  סך ימי א-ה בחודש: "&amp;חאזם!B6&amp;"  |  ימים שעברו: "&amp;חאזם!B7</f>
-        <v/>
+        <v>נכון לתאריך חישוב 16/08/26 | יום בדיקה: 15/08/26  |  סך ימי א-ה בחודש: 22  |  ימים שעברו: 10</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" s="49">
@@ -3295,262 +5345,262 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="49">
-      <c r="A5" s="82">
+      <c t="str" r="A5" s="82">
         <f>חאזם!B11</f>
-        <v/>
-      </c>
-      <c r="B5" s="83">
+        <v>בתי מרקחת פרטיים</v>
+      </c>
+      <c t="n" r="B5" s="83">
         <f>IF(חאזם!C11="","",חאזם!C11)</f>
-        <v/>
-      </c>
-      <c r="C5" s="83">
+        <v>109000</v>
+      </c>
+      <c t="n" r="C5" s="83">
         <f>חאזם!F11</f>
-        <v/>
-      </c>
-      <c r="D5" s="84">
+        <v>24608.1</v>
+      </c>
+      <c t="n" r="D5" s="84">
         <f>חאזם!G11</f>
-        <v/>
-      </c>
-      <c r="E5" s="83">
+        <v>0.225762385321101</v>
+      </c>
+      <c t="n" r="E5" s="83">
         <f>חאזם!H11</f>
-        <v/>
-      </c>
-      <c r="F5" s="83">
+        <v>84391.9</v>
+      </c>
+      <c t="n" r="F5" s="83">
         <f>חאזם!I11</f>
-        <v/>
-      </c>
-      <c r="G5" s="84">
+        <v>54137.82</v>
+      </c>
+      <c t="n" r="G5" s="84">
         <f>חאזם!J11</f>
-        <v/>
+        <v>0.496677247706422</v>
       </c>
       <c r="I5" s="85" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="49">
-      <c r="A6" s="82">
+      <c t="str" r="A6" s="82">
         <f>חאזם!B12</f>
-        <v/>
-      </c>
-      <c r="B6" s="83">
+        <v>BE</v>
+      </c>
+      <c t="n" r="B6" s="83">
         <f>IF(חאזם!C12="","",חאזם!C12)</f>
-        <v/>
-      </c>
-      <c r="C6" s="83">
+        <v>25070</v>
+      </c>
+      <c t="n" r="C6" s="83">
         <f>חאזם!F12</f>
-        <v/>
-      </c>
-      <c r="D6" s="84">
+        <v>10455.2</v>
+      </c>
+      <c t="n" r="D6" s="84">
         <f>חאזם!G12</f>
-        <v/>
-      </c>
-      <c r="E6" s="83">
+        <v>0.417040287195852</v>
+      </c>
+      <c t="n" r="E6" s="83">
         <f>חאזם!H12</f>
-        <v/>
-      </c>
-      <c r="F6" s="83">
+        <v>14614.8</v>
+      </c>
+      <c t="n" r="F6" s="83">
         <f>חאזם!I12</f>
-        <v/>
-      </c>
-      <c r="G6" s="84">
+        <v>23001.44</v>
+      </c>
+      <c t="n" r="G6" s="84">
         <f>חאזם!J12</f>
-        <v/>
+        <v>0.917488631830874</v>
       </c>
       <c r="I6" s="85" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="49">
-      <c r="A7" s="82">
+      <c t="str" r="A7" s="82">
         <f>חאזם!B13</f>
-        <v/>
-      </c>
-      <c r="B7" s="83">
+        <v>סופרפארם</v>
+      </c>
+      <c t="n" r="B7" s="83">
         <f>IF(חאזם!C13="","",חאזם!C13)</f>
-        <v/>
-      </c>
-      <c r="C7" s="83">
+        <v>119900</v>
+      </c>
+      <c t="n" r="C7" s="83">
         <f>חאזם!F13</f>
-        <v/>
-      </c>
-      <c r="D7" s="84">
+        <v>50294</v>
+      </c>
+      <c t="n" r="D7" s="84">
         <f>חאזם!G13</f>
-        <v/>
-      </c>
-      <c r="E7" s="83">
+        <v>0.419466221851543</v>
+      </c>
+      <c t="n" r="E7" s="83">
         <f>חאזם!H13</f>
-        <v/>
-      </c>
-      <c r="F7" s="83">
+        <v>69606</v>
+      </c>
+      <c t="n" r="F7" s="83">
         <f>חאזם!I13</f>
-        <v/>
-      </c>
-      <c r="G7" s="84">
+        <v>110646.8</v>
+      </c>
+      <c t="n" r="G7" s="84">
         <f>חאזם!J13</f>
-        <v/>
+        <v>0.922825688073394</v>
       </c>
       <c r="I7" s="85" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="49">
-      <c r="A8" s="82">
+      <c t="str" r="A8" s="82">
         <f>חאזם!B15</f>
-        <v/>
-      </c>
-      <c r="B8" s="83">
+        <v>מכוני אורטופדיה</v>
+      </c>
+      <c t="n" r="B8" s="83">
         <f>IF(חאזם!C15="","",חאזם!C15)</f>
-        <v/>
-      </c>
-      <c r="C8" s="83">
+        <v>47457</v>
+      </c>
+      <c t="n" r="C8" s="83">
         <f>חאזם!F15</f>
-        <v/>
-      </c>
-      <c r="D8" s="84">
+        <v>19629</v>
+      </c>
+      <c t="n" r="D8" s="84">
         <f>חאזם!G15</f>
-        <v/>
-      </c>
-      <c r="E8" s="83">
+        <v>0.413616537075669</v>
+      </c>
+      <c t="n" r="E8" s="83">
         <f>חאזם!H15</f>
-        <v/>
-      </c>
-      <c r="F8" s="83">
+        <v>27828</v>
+      </c>
+      <c t="n" r="F8" s="83">
         <f>חאזם!I15</f>
-        <v/>
-      </c>
-      <c r="G8" s="84">
+        <v>43183.8</v>
+      </c>
+      <c t="n" r="G8" s="84">
         <f>חאזם!J15</f>
-        <v/>
+        <v>0.909956381566471</v>
       </c>
       <c r="I8" s="85" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="49">
-      <c r="A9" s="82">
+      <c t="str" r="A9" s="82">
         <f>חאזם!B16</f>
-        <v/>
-      </c>
-      <c r="B9" s="83">
+        <v>מכוני פיזוטרפיה</v>
+      </c>
+      <c t="n" r="B9" s="83">
         <f>IF(חאזם!C16="","",חאזם!C16)</f>
-        <v/>
-      </c>
-      <c r="C9" s="83">
+        <v>17036</v>
+      </c>
+      <c t="n" r="C9" s="83">
         <f>חאזם!F16</f>
-        <v/>
-      </c>
-      <c r="D9" s="84">
+        <v>5352</v>
+      </c>
+      <c t="n" r="D9" s="84">
         <f>חאזם!G16</f>
-        <v/>
-      </c>
-      <c r="E9" s="83">
+        <v>0.314158253111059</v>
+      </c>
+      <c t="n" r="E9" s="83">
         <f>חאזם!H16</f>
-        <v/>
-      </c>
-      <c r="F9" s="83">
+        <v>11684</v>
+      </c>
+      <c t="n" r="F9" s="83">
         <f>חאזם!I16</f>
-        <v/>
-      </c>
-      <c r="G9" s="84">
+        <v>11774.4</v>
+      </c>
+      <c t="n" r="G9" s="84">
         <f>חאזם!J16</f>
-        <v/>
+        <v>0.69114815684433</v>
       </c>
       <c r="I9" s="85" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="49">
-      <c r="A10" s="82">
+      <c t="str" r="A10" s="82">
         <f>חאזם!B17</f>
-        <v/>
-      </c>
-      <c r="B10" s="83">
+        <v>מאוחדת</v>
+      </c>
+      <c t="n" r="B10" s="83">
         <f>IF(חאזם!C17="","",חאזם!C17)</f>
-        <v/>
-      </c>
-      <c r="C10" s="83">
+        <v>21800</v>
+      </c>
+      <c t="n" r="C10" s="83">
         <f>חאזם!F17</f>
-        <v/>
-      </c>
-      <c r="D10" s="84">
+        <v>6928.4</v>
+      </c>
+      <c t="n" r="D10" s="84">
         <f>חאזם!G17</f>
-        <v/>
-      </c>
-      <c r="E10" s="83">
+        <v>0.317816513761468</v>
+      </c>
+      <c t="n" r="E10" s="83">
         <f>חאזם!H17</f>
-        <v/>
-      </c>
-      <c r="F10" s="83">
+        <v>14871.6</v>
+      </c>
+      <c t="n" r="F10" s="83">
         <f>חאזם!I17</f>
-        <v/>
-      </c>
-      <c r="G10" s="84">
+        <v>15242.48</v>
+      </c>
+      <c t="n" r="G10" s="84">
         <f>חאזם!J17</f>
-        <v/>
+        <v>0.699196330275229</v>
       </c>
       <c r="I10" s="85" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="49">
-      <c r="A11" s="82">
+      <c t="str" r="A11" s="82">
         <f>חאזם!B18</f>
-        <v/>
-      </c>
-      <c r="B11" s="83">
+        <v>חנויות פרטיות</v>
+      </c>
+      <c t="n" r="B11" s="83">
         <f>IF(חאזם!C18="","",חאזם!C18)</f>
-        <v/>
-      </c>
-      <c r="C11" s="83">
+        <v>6250</v>
+      </c>
+      <c t="n" r="C11" s="83">
         <f>חאזם!F18</f>
-        <v/>
-      </c>
-      <c r="D11" s="84">
+        <v>0</v>
+      </c>
+      <c t="n" r="D11" s="84">
         <f>חאזם!G18</f>
-        <v/>
-      </c>
-      <c r="E11" s="83">
+        <v>0</v>
+      </c>
+      <c t="n" r="E11" s="83">
         <f>חאזם!H18</f>
-        <v/>
-      </c>
-      <c r="F11" s="83">
+        <v>6250</v>
+      </c>
+      <c t="n" r="F11" s="83">
         <f>חאזם!I18</f>
-        <v/>
-      </c>
-      <c r="G11" s="84">
+        <v>0</v>
+      </c>
+      <c t="n" r="G11" s="84">
         <f>חאזם!J18</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I11" s="85" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="49">
-      <c r="A12" s="82">
+      <c t="str" r="A12" s="82">
         <f>חאזם!B19</f>
-        <v/>
-      </c>
-      <c r="B12" s="83">
+        <v>חנויות ספורט</v>
+      </c>
+      <c t="str" r="B12" s="83">
         <f>IF(חאזם!C19="","",חאזם!C19)</f>
         <v/>
       </c>
-      <c r="C12" s="83">
+      <c t="n" r="C12" s="83">
         <f>חאזם!F19</f>
-        <v/>
-      </c>
-      <c r="D12" s="84">
+        <v>1276</v>
+      </c>
+      <c t="str" r="D12" s="84">
         <f>חאזם!G19</f>
         <v/>
       </c>
-      <c r="E12" s="83">
+      <c t="str" r="E12" s="83">
         <f>חאזם!H19</f>
         <v/>
       </c>
-      <c r="F12" s="83">
+      <c t="n" r="F12" s="83">
         <f>חאזם!I19</f>
-        <v/>
-      </c>
-      <c r="G12" s="84">
+        <v>2807.2</v>
+      </c>
+      <c t="str" r="G12" s="84">
         <f>חאזם!J19</f>
         <v/>
       </c>
@@ -3559,93 +5609,93 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="49">
-      <c r="A13" s="86">
+      <c t="str" r="A13" s="86">
         <f>חאזם!B14</f>
-        <v/>
-      </c>
-      <c r="B13" s="87">
+        <v>סה"כ</v>
+      </c>
+      <c t="n" r="B13" s="87">
         <f>IF(חאזם!C14="","",חאזם!C14)</f>
-        <v/>
-      </c>
-      <c r="C13" s="87">
+        <v>253970</v>
+      </c>
+      <c t="n" r="C13" s="87">
         <f>חאזם!F14</f>
-        <v/>
-      </c>
-      <c r="D13" s="88">
+        <v>85357.3</v>
+      </c>
+      <c t="n" r="D13" s="88">
         <f>חאזם!G14</f>
-        <v/>
-      </c>
-      <c r="E13" s="87">
+        <v>0.3360920581171</v>
+      </c>
+      <c t="n" r="E13" s="87">
         <f>חאזם!H14</f>
-        <v/>
-      </c>
-      <c r="F13" s="87">
+        <v>168612.7</v>
+      </c>
+      <c t="n" r="F13" s="87">
         <f>חאזם!I14</f>
-        <v/>
-      </c>
-      <c r="G13" s="88">
+        <v>187786.06</v>
+      </c>
+      <c t="n" r="G13" s="88">
         <f>חאזם!J14</f>
-        <v/>
+        <v>0.739402527857621</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="49">
-      <c r="A14" s="86">
+      <c t="str" r="A14" s="86">
         <f>חאזם!B20</f>
-        <v/>
-      </c>
-      <c r="B14" s="87">
+        <v>סה"כ</v>
+      </c>
+      <c t="n" r="B14" s="87">
         <f>IF(חאזם!C20="","",חאזם!C20)</f>
-        <v/>
-      </c>
-      <c r="C14" s="87">
+        <v>92543</v>
+      </c>
+      <c t="n" r="C14" s="87">
         <f>חאזם!F20</f>
-        <v/>
-      </c>
-      <c r="D14" s="88">
+        <v>33185.4</v>
+      </c>
+      <c t="n" r="D14" s="88">
         <f>חאזם!G20</f>
-        <v/>
-      </c>
-      <c r="E14" s="87">
+        <v>0.358594383151616</v>
+      </c>
+      <c t="n" r="E14" s="87">
         <f>חאזם!H20</f>
-        <v/>
-      </c>
-      <c r="F14" s="87">
+        <v>59357.6</v>
+      </c>
+      <c t="n" r="F14" s="87">
         <f>חאזם!I20</f>
-        <v/>
-      </c>
-      <c r="G14" s="88">
+        <v>73007.88</v>
+      </c>
+      <c t="n" r="G14" s="88">
         <f>חאזם!J20</f>
-        <v/>
+        <v>0.788907642933555</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="49">
-      <c r="A15" s="89">
+      <c t="str" r="A15" s="89">
         <f>חאזם!B21</f>
-        <v/>
-      </c>
-      <c r="B15" s="90">
+        <v>סה"כ כללי</v>
+      </c>
+      <c t="n" r="B15" s="90">
         <f>IF(חאזם!C21="","",חאזם!C21)</f>
-        <v/>
-      </c>
-      <c r="C15" s="90">
+        <v>346513</v>
+      </c>
+      <c t="n" r="C15" s="90">
         <f>חאזם!F21</f>
-        <v/>
-      </c>
-      <c r="D15" s="91">
+        <v>118542.7</v>
+      </c>
+      <c t="n" r="D15" s="91">
         <f>חאזם!G21</f>
-        <v/>
-      </c>
-      <c r="E15" s="90">
+        <v>0.342101739328683</v>
+      </c>
+      <c t="n" r="E15" s="90">
         <f>חאזם!H21</f>
-        <v/>
-      </c>
-      <c r="F15" s="90">
+        <v>227970.3</v>
+      </c>
+      <c t="n" r="F15" s="90">
         <f>חאזם!I21</f>
-        <v/>
-      </c>
-      <c r="G15" s="91">
+        <v>260793.94</v>
+      </c>
+      <c t="n" r="G15" s="91">
         <f>חאזם!J21</f>
-        <v/>
+        <v>0.752623826523103</v>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1" s="49">

--- a/kirill/outputs/hazam-tracking-dashboard.xlsx
+++ b/kirill/outputs/hazam-tracking-dashboard.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="53">
   <si>
     <t xml:space="preserve">מעקב ביצועי סוכן חאזם</t>
   </si>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">ימים שנותרו</t>
   </si>
   <si>
-    <t xml:space="preserve">הערות: (1) "יעד חודשי", "מכירות עד לבדיקה", "ימים שנותרו" ו"יעד יומי נדרש" נמשכים בנוסחה חיה מבלוק הסיכום (שורה 21, ושורות 25-26) בגיליון כל סוכן. (2) "ימים שנותרו" זהה לכל הסוכנים (אותו חודש ואותו יום בדיקה) ולכן שורת "סה"כ כללי" מציגה את אותו המספר, לא סכום. (3) עיצוב מותנה על עמודת "אחוז ביצוע": אדום מתחת ל-33%, צהוב 33%-66%, ירוק מעל 66% — זהה לעיצוב שבכל גיליון סוכן.</t>
+    <t xml:space="preserve">הערות: (1) "יעד חודשי", "מכירות עד לבדיקה", "ימים שנותרו" ו"יעד יומי נדרש" נמשכים בנוסחה חיה מבלוק הסיכום (שורה 21, ושורות 25-26) בגיליון כל סוכן. (2) "ימים שנותרו" זהה לכל הסוכנים (אותו חודש ואותו יום בדיקה) ולכן שורת "סה"כ כללי" מציגה את אותו המספר, לא סכום. (3) עיצוב מותנה על עמודת "אחוז ביצוע": אדום מתחת ל-33%, צהוב 33%-66%, ירוק מעל 66% — זהה לעיצוב שבכל גיליון סוכן. (4) עמודת "קצב %" = תחזית סיום חודש (אם ממשיכים באותו קצב מכירות יומי ממוצע עד כה) חלקי היעד החודשי, נמשכת בנוסחה חיה מעמודה J שורה 21 בגיליון כל סוכן. עיצוב מותנה על עמודה זו: אדום מתחת ל-80% (לא צפויים לעמוד ביעד), צהוב 80%-100% (גבולי), ירוק מעל 100% (צפויים לעמוד/לעבור את היעד) — סף שונה מעמודת "אחוז ביצוע" כי כאן ההשוואה היא מול 100% מהיעד (תחזית), לא מול אמצע החודש. שורת "סה"כ כללי" בעמודה זו = סכום תחזיות ה-₪ של כל 4 הסוכנים חלקי סכום היעדים (B10), לא ממוצע של אחוזי הקצב הבודדים.</t>
   </si>
   <si>
     <t xml:space="preserve">גרף - השוואת אחוז ביצוע בין סוכנים</t>
@@ -197,7 +197,7 @@
     <numFmt numFmtId="168" formatCode="0%"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -332,26 +332,6 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="FreeSans"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="FreeSans"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -774,14 +754,14 @@
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF4F81BD"/>
+      <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF63BE7B"/>
       <rgbColor rgb="FF92D050"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FFB3B3B3"/>
+      <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF548235"/>
       <rgbColor rgb="FF003300"/>
@@ -3874,13 +3854,13 @@
     <tabColor rgb="FF548235"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3892,6 +3872,7 @@
       <c r="D1" s="31"/>
       <c r="E1" s="31"/>
       <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="str">
@@ -3903,6 +3884,7 @@
       <c r="D2" s="32"/>
       <c r="E2" s="32"/>
       <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
     </row>
     <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
@@ -3913,6 +3895,7 @@
       <c r="D3" s="33"/>
       <c r="E3" s="33"/>
       <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="34" t="s">
@@ -3928,9 +3911,12 @@
         <v>49</v>
       </c>
       <c r="E5" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="G5" s="34" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3951,11 +3937,15 @@
         <f aca="false">חאזם!G21</f>
         <v>0.342101739328683</v>
       </c>
-      <c r="E6" s="38" t="n">
+      <c r="E6" s="37" t="n">
+        <f aca="false">חאזם!J21</f>
+        <v>0.752623826523103</v>
+      </c>
+      <c r="F6" s="38" t="n">
         <f aca="false">חאזם!A26</f>
         <v>12</v>
       </c>
-      <c r="F6" s="36" t="n">
+      <c r="G6" s="36" t="n">
         <f aca="false">חאזם!D26</f>
         <v>18997.525</v>
       </c>
@@ -3977,11 +3967,15 @@
         <f aca="false">דודו!G21</f>
         <v>0.480464301909609</v>
       </c>
-      <c r="E7" s="38" t="n">
+      <c r="E7" s="37" t="n">
+        <f aca="false">דודו!J21</f>
+        <v>1.05702146420114</v>
+      </c>
+      <c r="F7" s="38" t="n">
         <f aca="false">דודו!A26</f>
         <v>12</v>
       </c>
-      <c r="F7" s="36" t="n">
+      <c r="G7" s="36" t="n">
         <f aca="false">דודו!D26</f>
         <v>13748.3</v>
       </c>
@@ -4003,11 +3997,15 @@
         <f aca="false">חיים!G21</f>
         <v>0.370892343773642</v>
       </c>
-      <c r="E8" s="38" t="n">
+      <c r="E8" s="37" t="n">
+        <f aca="false">חיים!J21</f>
+        <v>0.815963156302012</v>
+      </c>
+      <c r="F8" s="38" t="n">
         <f aca="false">חיים!A26</f>
         <v>12</v>
       </c>
-      <c r="F8" s="36" t="n">
+      <c r="G8" s="36" t="n">
         <f aca="false">חיים!D26</f>
         <v>13859.2416666667</v>
       </c>
@@ -4029,11 +4027,15 @@
         <f aca="false">סטאס!G21</f>
         <v>0.34403129060115</v>
       </c>
-      <c r="E9" s="38" t="n">
+      <c r="E9" s="37" t="n">
+        <f aca="false">סטאס!J21</f>
+        <v>0.75686883932253</v>
+      </c>
+      <c r="F9" s="38" t="n">
         <f aca="false">סטאס!A26</f>
         <v>12</v>
       </c>
-      <c r="F9" s="36" t="n">
+      <c r="G9" s="36" t="n">
         <f aca="false">סטאס!D26</f>
         <v>14052.7083333333</v>
       </c>
@@ -4054,12 +4056,16 @@
         <f aca="false">IFERROR(C10/B10,"")</f>
         <v>0.386002603123242</v>
       </c>
-      <c r="E10" s="42" t="n">
-        <f aca="false">E6</f>
+      <c r="E10" s="41" t="n">
+        <f aca="false">IFERROR((חאזם!I21+דודו!I21+חיים!I21+סטאס!I21)/B10,"")</f>
+        <v>0.849205726871132</v>
+      </c>
+      <c r="F10" s="42" t="n">
+        <f aca="false">F6</f>
         <v>12</v>
       </c>
-      <c r="F10" s="40" t="n">
-        <f aca="false">IFERROR((B10-C10)/E10,"")</f>
+      <c r="G10" s="40" t="n">
+        <f aca="false">IFERROR((B10-C10)/F10,"")</f>
         <v>60657.775</v>
       </c>
     </row>
@@ -4072,6 +4078,7 @@
       <c r="D12" s="43"/>
       <c r="E12" s="43"/>
       <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="44" t="s">
@@ -4082,14 +4089,15 @@
       <c r="D14" s="44"/>
       <c r="E14" s="44"/>
       <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D10">
     <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
@@ -4102,6 +4110,17 @@
       <formula>0.66</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E6:E10">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/kirill/outputs/hazam-tracking-dashboard.xlsx
+++ b/kirill/outputs/hazam-tracking-dashboard.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="54">
   <si>
     <t xml:space="preserve">מעקב ביצועי סוכן חאזם</t>
   </si>
@@ -176,13 +176,16 @@
     <t xml:space="preserve">אחוז ביצוע</t>
   </si>
   <si>
-    <t xml:space="preserve">ימים שנותרו</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערות: (1) "יעד חודשי", "מכירות עד לבדיקה", "ימים שנותרו" ו"יעד יומי נדרש" נמשכים בנוסחה חיה מבלוק הסיכום (שורה 21, ושורות 25-26) בגיליון כל סוכן. (2) "ימים שנותרו" זהה לכל הסוכנים (אותו חודש ואותו יום בדיקה) ולכן שורת "סה"כ כללי" מציגה את אותו המספר, לא סכום. (3) עיצוב מותנה על עמודת "אחוז ביצוע": אדום מתחת ל-33%, צהוב 33%-66%, ירוק מעל 66% — זהה לעיצוב שבכל גיליון סוכן. (4) עמודת "קצב %" = תחזית סיום חודש (אם ממשיכים באותו קצב מכירות יומי ממוצע עד כה) חלקי היעד החודשי, נמשכת בנוסחה חיה מעמודה J שורה 21 בגיליון כל סוכן. עיצוב מותנה על עמודה זו: אדום מתחת ל-80% (לא צפויים לעמוד ביעד), צהוב 80%-100% (גבולי), ירוק מעל 100% (צפויים לעמוד/לעבור את היעד) — סף שונה מעמודת "אחוז ביצוע" כי כאן ההשוואה היא מול 100% מהיעד (תחזית), לא מול אמצע החודש. שורת "סה"כ כללי" בעמודה זו = סכום תחזיות ה-₪ של כל 4 הסוכנים חלקי סכום היעדים (B10), לא ממוצע של אחוזי הקצב הבודדים.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">גרף - השוואת אחוז ביצוע בין סוכנים</t>
+    <t xml:space="preserve">% הגעה ליעד לפי קצב נוכחי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ימים נותרים לעבודה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">יעד כספי יומי נדרש להגעה ל-100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערות: (1) "יעד חודשי", "מכירות עד לבדיקה", "ימים נותרים לעבודה" ו"יעד כספי יומי נדרש להגעה ל-100%" נמשכים בנוסחה חיה מבלוק הסיכום (שורה 21, ושורות 25-26) בגיליון כל סוכן. עמודת "יעד כספי יומי נדרש להגעה ל-100%" = (יעד חודשי − מכירות עד לבדיקה) / ימים נותרים לעבודה (בגיליון הסוכן: =H21/(B6-B7), כאשר H21=C21-F21 הוא הפער ליעד, ו-B6-B7 הם ימי א'-ה' שנותרו עד סוף החודש) — כלומר כמה עוד יש למכור בממוצע בכל יום עבודה נותר כדי להגיע בדיוק ל-100% מהיעד החודשי. (2) "ימים נותרים לעבודה" זהה לכל הסוכנים (אותו חודש ואותו יום בדיקה) ולכן שורת "סה"כ כללי" מציגה את אותו המספר, לא סכום. (3) עיצוב מותנה על עמודת "אחוז ביצוע": אדום מתחת ל-33%, צהוב 33%-66%, ירוק מעל 66% — זהה לעיצוב שבכל גיליון סוכן. (4) עמודת "% הגעה ליעד לפי קצב נוכחי" = תחזית סיום חודש (אם ממשיכים באותו קצב מכירות יומי ממוצע עד כה) חלקי היעד החודשי, נמשכת בנוסחה חיה מעמודה J שורה 21 בגיליון כל סוכן. עיצוב מותנה על עמודה זו: אדום מתחת ל-80% (לא צפויים לעמוד ביעד), צהוב 80%-100% (גבולי), ירוק מעל 100% (צפויים לעמוד/לעבור את היעד) — סף שונה מעמודת "אחוז ביצוע" כי כאן ההשוואה היא מול 100% מהיעד (תחזית), לא מול אמצע החודש. שורת "סה"כ כללי" בעמודה זו = סכום תחזיות ה-₪ של כל 4 הסוכנים חלקי סכום היעדים (B10), לא ממוצע של אחוזי הקצב הבודדים.</t>
   </si>
 </sst>
 </file>
@@ -433,7 +436,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -608,10 +611,6 @@
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -773,362 +772,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>אחוז ביצוע לפי סוכן</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>DASHBOARD!D5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>אחוז ביצוע</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:numFmt formatCode="0.0%" sourceLinked="1"/>
-            <c:txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="1"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="1"/>
-            <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>DASHBOARD!$A$6:$A$9</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>חאזם</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>דודו</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>חיים</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>סטאס</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>DASHBOARD!$D$6:$D$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.342101739328683</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.480464301909609</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.370892343773642</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.34403129060115</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
-        <c:axId val="65546120"/>
-        <c:axId val="16085936"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="65546120"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>סוכן</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
-            </a:solidFill>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="16085936"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="16085936"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="0">
-              <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>אחוז ביצוע</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="0%" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
-            </a:solidFill>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="65546120"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="ffffff"/>
-    </a:solidFill>
-    <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-  </c:spPr>
-</c:chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>-70200</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>22320</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="-5759640" y="4229280"/>
-        <a:ext cx="5759640" cy="2879640"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3854,13 +3497,13 @@
     <tabColor rgb="FF548235"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3911,13 +3554,13 @@
         <v>49</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4071,7 +3714,7 @@
     </row>
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="43" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B12" s="43"/>
       <c r="C12" s="43"/>
@@ -4080,24 +3723,12 @@
       <c r="F12" s="43"/>
       <c r="G12" s="43"/>
     </row>
-    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="44" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D10">
     <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
@@ -4128,6 +3759,5 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/kirill/outputs/hazam-tracking-dashboard.xlsx
+++ b/kirill/outputs/hazam-tracking-dashboard.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="חאזם" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="59">
   <si>
     <t xml:space="preserve">מעקב ביצועי סוכן חאזם</t>
   </si>
@@ -47,76 +47,103 @@
     <t xml:space="preserve">ימי א'-ה' שעברו (מ-1 בחודש עד יום הבדיקה):</t>
   </si>
   <si>
-    <t xml:space="preserve">הערה: עמודות D ('מכירות') ו-E ('פתוחות') הן צילום מצב (snapshot) של הערכים האחרונים שנשמרו בקאש של קובץ המקור שהועלה (hazam-tracking-source.xlsx). בקובץ המקור עמודות אלה היו מקושרות לקובץ אקסל חיצוני שבור (קישורי '[1]מכירות!...' / '[1]פתוחות!...') שאין אליו גישה כעת - לכן הוחלפו כאן בערכים קשיחים מהקאש. זה אינו לינק חי. אם יש קובץ מקור מעודכן יותר, יש לספק אותו לעדכון.</t>
+    <t xml:space="preserve">סוכן</t>
+  </si>
+  <si>
+    <t xml:space="preserve">קטגוריה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">יעד חודשי (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מכירות (snapshot)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פתוחות (snapshot)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מכירות עד לבדיקה (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אחוז ביצוע לפי יעד</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כמה נשאר לסיום החודש (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">קצב אומדן סוף חודש (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">קצב %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חאזם</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בתי מרקחת פרטיים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סופרפארם</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סה"כ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מכוני אורטופדיה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מכוני פיזוטרפיה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מאוחדת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חנויות פרטיות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חנויות ספורט</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סה"כ כללי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סיכום ביצועים — סה"כ כללי (חאזם)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ימים שעברו</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ממוצע מכירות יומי (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">קצב (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הגעה ל-100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ימים שנותרו</t>
+  </si>
+  <si>
+    <t xml:space="preserve">יעד ממוצע ליום (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מעקב ביצועי סוכן דודו</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערה: עמודות D ('מכירות') ו-E ('פתוחות') הן צילום מצב (snapshot) של הערכים המחושבים (קאש) שכבר קיימים בקובץ המקור שהועלה (agents-tracking-source-full.xlsx, גיליון 'דודו'), שם הם תוצאה של נוסחאות פנימיות מול גיליונות 'מכירות'/'פתוחות' באותו קובץ. הועתקו לכאן כערכים קשיחים (לא לינק חי), בהתאם לאותה שיטה שבה נבנה גיליון חאזם. לתשומת לב - פער בנתוני המקור: לא נמצא יעד חודשי (עמודה C) לקטגוריות: מכוני פיזוטרפיה; חנויות ספורט. עד להשלמה ידנית, אחוז ביצוע וקצב % לקטגוריות אלה יוצגו כריק.</t>
   </si>
   <si>
     <t xml:space="preserve">גיליון זה = נתוני מקור וחישוב (Working Data): כל הנוסחאות, המקור וה-snapshot המלאים נמצאים כאן. לתצוגת סיכום ויזואלית עם גרפים למנהל  ⇦  עבור לגיליון DASHBOARD.</t>
   </si>
   <si>
-    <t xml:space="preserve">סוכן</t>
-  </si>
-  <si>
-    <t xml:space="preserve">קטגוריה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">יעד חודשי (₪)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מכירות (snapshot)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">פתוחות (snapshot)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מכירות עד לבדיקה (₪)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">אחוז ביצוע לפי יעד</t>
-  </si>
-  <si>
-    <t xml:space="preserve">כמה נשאר לסיום החודש (₪)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">קצב אומדן סוף חודש (₪)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">קצב %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חאזם</t>
-  </si>
-  <si>
-    <t xml:space="preserve">בתי מרקחת פרטיים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סופרפארם</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סה"כ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מכוני אורטופדיה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מכוני פיזוטרפיה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מאוחדת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חנויות פרטיות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חנויות ספורט</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סה"כ כללי</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סיכום ביצועים — סה"כ כללי (חאזם)</t>
+    <t xml:space="preserve">דודו</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סיכום ביצועים — סה"כ כללי (דודו)</t>
   </si>
   <si>
     <t xml:space="preserve">ימים שנותרו (א'-ה', עד סוף החודש)</t>
@@ -129,18 +156,6 @@
   </si>
   <si>
     <t xml:space="preserve">הערה: "ימים שנותרו" = סה"כ ימי א'-ה' בחודש (B6) פחות ימי א'-ה' שעברו עד יום הבדיקה (B7). "יעד יומי נדרש" = הסכום שנותר להשלמת היעד הכללי (H21) חלקי הימים שנותרו. עיצוב מותנה על תא האחוז: אדום מתחת ל-33%, צהוב 33%-66%, ירוק מעל 66%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מעקב ביצועי סוכן דודו</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערה: עמודות D ('מכירות') ו-E ('פתוחות') הן צילום מצב (snapshot) של הערכים המחושבים (קאש) שכבר קיימים בקובץ המקור שהועלה (agents-tracking-source-full.xlsx, גיליון 'דודו'), שם הם תוצאה של נוסחאות פנימיות מול גיליונות 'מכירות'/'פתוחות' באותו קובץ. הועתקו לכאן כערכים קשיחים (לא לינק חי), בהתאם לאותה שיטה שבה נבנה גיליון חאזם. לתשומת לב - פער בנתוני המקור: לא נמצא יעד חודשי (עמודה C) לקטגוריות: מכוני פיזוטרפיה; חנויות ספורט. עד להשלמה ידנית, אחוז ביצוע וקצב % לקטגוריות אלה יוצגו כריק.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">דודו</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סיכום ביצועים — סה"כ כללי (דודו)</t>
   </si>
   <si>
     <t xml:space="preserve">מעקב ביצועי סוכן חיים</t>
@@ -192,15 +207,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * \-??_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="0%"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="General"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,18 +263,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <i val="true"/>
-      <sz val="10.5"/>
-      <color rgb="FF1F4E78"/>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -288,9 +293,17 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <i val="true"/>
       <sz val="9"/>
-      <color rgb="FF595959"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -299,6 +312,14 @@
       <b val="true"/>
       <sz val="10.5"/>
       <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -337,7 +358,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -352,20 +373,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDCE6F1"/>
-        <bgColor rgb="FFE2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
         <bgColor rgb="FF003366"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -382,12 +391,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.3999"/>
+        <bgColor rgb="FFCC99FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
         <bgColor rgb="FFDCE6F1"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -410,6 +437,13 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -436,7 +470,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="55">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -453,131 +487,175 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -593,23 +671,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -750,7 +828,7 @@
       <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFFEB84"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFD99694"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
@@ -958,7 +1036,7 @@
   <dimension ref="A1:J41"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
@@ -995,7 +1073,7 @@
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="4" t="n">
         <v>46249</v>
       </c>
     </row>
@@ -1021,7 +1099,7 @@
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="5" t="n">
         <f aca="true">SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B5)))&lt;6)*1)</f>
         <v>22</v>
       </c>
@@ -1030,527 +1108,572 @@
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="5" t="n">
         <f aca="true">SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B3)))&lt;6)*1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>9</v>
       </c>
+      <c r="D9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="B10" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="9" t="s">
         <v>18</v>
       </c>
+      <c r="C10" s="10" t="n">
+        <v>109000</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>20013.1</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>4595</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <f aca="false">D10+E10</f>
+        <v>24608.1</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <f aca="false">IFERROR(F10/C10,"")</f>
+        <v>0.225762385321101</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <f aca="false">IF(C10="","",C10-F10)</f>
+        <v>84391.9</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <f aca="false">IFERROR((F10/$B$7)*$B$6,"")</f>
+        <v>54137.82</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <f aca="false">IFERROR(I10/C10,"")</f>
+        <v>0.496677247706422</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="C11" s="10" t="n">
+        <v>25070</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>9809.2</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>646</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <f aca="false">D11+E11</f>
+        <v>10455.2</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <f aca="false">IFERROR(F11/C11,"")</f>
+        <v>0.417040287195852</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <f aca="false">IF(C11="","",C11-F11)</f>
+        <v>14614.8</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <f aca="false">IFERROR((F11/$B$7)*$B$6,"")</f>
+        <v>23001.44</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <f aca="false">IFERROR(I11/C11,"")</f>
+        <v>0.917488631830874</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="12" t="n">
-        <v>109000</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>20013.1</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>4595</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <f aca="false">D11+E11</f>
-        <v>24608.1</v>
-      </c>
-      <c r="G11" s="14" t="n">
-        <f aca="false">IFERROR(F11/C11,"")</f>
-        <v>0.225762385321101</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <f aca="false">IF(C11="","",C11-F11)</f>
-        <v>84391.9</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <f aca="false">IFERROR((F11/$B$7)*$B$6,"")</f>
-        <v>54137.82</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <f aca="false">IFERROR(I11/C11,"")</f>
-        <v>0.496677247706422</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11" t="s">
+      <c r="C12" s="10" t="n">
+        <v>119900</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>50294</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="11" t="n">
+        <f aca="false">D12+E12</f>
+        <v>50294</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <f aca="false">IFERROR(F12/C12,"")</f>
+        <v>0.419466221851543</v>
+      </c>
+      <c r="H12" s="11" t="n">
+        <f aca="false">IF(C12="","",C12-F12)</f>
+        <v>69606</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <f aca="false">IFERROR((F12/$B$7)*$B$6,"")</f>
+        <v>110646.8</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <f aca="false">IFERROR(I12/C12,"")</f>
+        <v>0.922825688073394</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8"/>
+      <c r="B13" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="12" t="n">
-        <v>25070</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>9809.2</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>646</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <f aca="false">D12+E12</f>
-        <v>10455.2</v>
-      </c>
-      <c r="G12" s="14" t="n">
-        <f aca="false">IFERROR(F12/C12,"")</f>
-        <v>0.417040287195852</v>
-      </c>
-      <c r="H12" s="13" t="n">
-        <f aca="false">IF(C12="","",C12-F12)</f>
-        <v>14614.8</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <f aca="false">IFERROR((F12/$B$7)*$B$6,"")</f>
-        <v>23001.44</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <f aca="false">IFERROR(I12/C12,"")</f>
-        <v>0.917488631830874</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11" t="s">
+      <c r="C13" s="14" t="n">
+        <f aca="false">SUM(C10:C12)</f>
+        <v>253970</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <f aca="false">SUM(D10:D12)</f>
+        <v>80116.3</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <f aca="false">SUM(E10:E12)</f>
+        <v>5241</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <f aca="false">SUM(F10:F12)</f>
+        <v>85357.3</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <f aca="false">IFERROR(F13/C13,"")</f>
+        <v>0.3360920581171</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <f aca="false">IF(C13="","",C13-F13)</f>
+        <v>168612.7</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <f aca="false">IFERROR((F13/$B$7)*$B$6,"")</f>
+        <v>187786.06</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <f aca="false">IFERROR(I13/C13,"")</f>
+        <v>0.739402527857621</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8"/>
+      <c r="B14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="12" t="n">
-        <v>119900</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>50294</v>
-      </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="13" t="n">
-        <f aca="false">D13+E13</f>
-        <v>50294</v>
-      </c>
-      <c r="G13" s="14" t="n">
-        <f aca="false">IFERROR(F13/C13,"")</f>
-        <v>0.419466221851543</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <f aca="false">IF(C13="","",C13-F13)</f>
-        <v>69606</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <f aca="false">IFERROR((F13/$B$7)*$B$6,"")</f>
-        <v>110646.8</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <f aca="false">IFERROR(I13/C13,"")</f>
-        <v>0.922825688073394</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="15" t="s">
+      <c r="C14" s="10" t="n">
+        <v>47457</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>19629</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="11" t="n">
+        <f aca="false">D14+E14</f>
+        <v>19629</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <f aca="false">IFERROR(F14/C14,"")</f>
+        <v>0.413616537075669</v>
+      </c>
+      <c r="H14" s="11" t="n">
+        <f aca="false">IF(C14="","",C14-F14)</f>
+        <v>27828</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <f aca="false">IFERROR((F14/$B$7)*$B$6,"")</f>
+        <v>43183.8</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <f aca="false">IFERROR(I14/C14,"")</f>
+        <v>0.909956381566471</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="16" t="n">
-        <f aca="false">SUM(C11:C13)</f>
-        <v>253970</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <f aca="false">SUM(D11:D13)</f>
-        <v>80116.3</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <f aca="false">SUM(E11:E13)</f>
-        <v>5241</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <f aca="false">SUM(F11:F13)</f>
-        <v>85357.3</v>
-      </c>
-      <c r="G14" s="17" t="n">
-        <f aca="false">IFERROR(F14/C14,"")</f>
-        <v>0.3360920581171</v>
-      </c>
-      <c r="H14" s="16" t="n">
-        <f aca="false">IF(C14="","",C14-F14)</f>
-        <v>168612.7</v>
-      </c>
-      <c r="I14" s="16" t="n">
-        <f aca="false">IFERROR((F14/$B$7)*$B$6,"")</f>
-        <v>187786.06</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <f aca="false">IFERROR(I14/C14,"")</f>
-        <v>0.739402527857621</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>47457</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>19629</v>
-      </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="13" t="n">
-        <f aca="false">D15+E15</f>
-        <v>19629</v>
-      </c>
-      <c r="G15" s="14" t="n">
-        <f aca="false">IFERROR(F15/C15,"")</f>
-        <v>0.413616537075669</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <f aca="false">IF(C15="","",C15-F15)</f>
-        <v>27828</v>
-      </c>
-      <c r="I15" s="13" t="n">
-        <f aca="false">IFERROR((F15/$B$7)*$B$6,"")</f>
-        <v>43183.8</v>
-      </c>
-      <c r="J15" s="14" t="n">
-        <f aca="false">IFERROR(I15/C15,"")</f>
-        <v>0.909956381566471</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="C15" s="10" t="n">
         <f aca="false">16734+302</f>
         <v>17036</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D15" s="10" t="n">
         <v>5352</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="13" t="n">
+      <c r="E15" s="10"/>
+      <c r="F15" s="11" t="n">
+        <f aca="false">D15+E15</f>
+        <v>5352</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <f aca="false">IFERROR(F15/C15,"")</f>
+        <v>0.314158253111059</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <f aca="false">IF(C15="","",C15-F15)</f>
+        <v>11684</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <f aca="false">IFERROR((F15/$B$7)*$B$6,"")</f>
+        <v>11774.4</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <f aca="false">IFERROR(I15/C15,"")</f>
+        <v>0.69114815684433</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>21800</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>6626.4</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>302</v>
+      </c>
+      <c r="F16" s="11" t="n">
         <f aca="false">D16+E16</f>
-        <v>5352</v>
-      </c>
-      <c r="G16" s="14" t="n">
+        <v>6928.4</v>
+      </c>
+      <c r="G16" s="12" t="n">
         <f aca="false">IFERROR(F16/C16,"")</f>
-        <v>0.314158253111059</v>
-      </c>
-      <c r="H16" s="13" t="n">
+        <v>0.317816513761468</v>
+      </c>
+      <c r="H16" s="11" t="n">
         <f aca="false">IF(C16="","",C16-F16)</f>
-        <v>11684</v>
-      </c>
-      <c r="I16" s="13" t="n">
+        <v>14871.6</v>
+      </c>
+      <c r="I16" s="11" t="n">
         <f aca="false">IFERROR((F16/$B$7)*$B$6,"")</f>
-        <v>11774.4</v>
-      </c>
-      <c r="J16" s="14" t="n">
+        <v>15242.48</v>
+      </c>
+      <c r="J16" s="12" t="n">
         <f aca="false">IFERROR(I16/C16,"")</f>
-        <v>0.69114815684433</v>
+        <v>0.699196330275229</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11" t="s">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>6250</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="11" t="n">
+        <f aca="false">D17+E17</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <f aca="false">IFERROR(F17/C17,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <f aca="false">IF(C17="","",C17-F17)</f>
+        <v>6250</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <f aca="false">IFERROR((F17/$B$7)*$B$6,"")</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <f aca="false">IFERROR(I17/C17,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="12" t="n">
-        <v>21800</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>6626.4</v>
-      </c>
-      <c r="E17" s="12" t="n">
+      <c r="C18" s="10"/>
+      <c r="D18" s="10" t="n">
+        <v>1276</v>
+      </c>
+      <c r="E18" s="10"/>
+      <c r="F18" s="11" t="n">
+        <f aca="false">D18+E18</f>
+        <v>1276</v>
+      </c>
+      <c r="G18" s="12" t="str">
+        <f aca="false">IFERROR(F18/C18,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="11" t="str">
+        <f aca="false">IF(C18="","",C18-F18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="11" t="n">
+        <f aca="false">IFERROR((F18/$B$7)*$B$6,"")</f>
+        <v>2807.2</v>
+      </c>
+      <c r="J18" s="12" t="str">
+        <f aca="false">IFERROR(I18/C18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <f aca="false">SUM(C14:C18)</f>
+        <v>92543</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <f aca="false">SUM(D14:D18)</f>
+        <v>32883.4</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <f aca="false">SUM(E14:E18)</f>
         <v>302</v>
       </c>
-      <c r="F17" s="13" t="n">
-        <f aca="false">D17+E17</f>
-        <v>6928.4</v>
-      </c>
-      <c r="G17" s="14" t="n">
-        <f aca="false">IFERROR(F17/C17,"")</f>
-        <v>0.317816513761468</v>
-      </c>
-      <c r="H17" s="13" t="n">
-        <f aca="false">IF(C17="","",C17-F17)</f>
-        <v>14871.6</v>
-      </c>
-      <c r="I17" s="13" t="n">
-        <f aca="false">IFERROR((F17/$B$7)*$B$6,"")</f>
-        <v>15242.48</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <f aca="false">IFERROR(I17/C17,"")</f>
-        <v>0.699196330275229</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11" t="s">
+      <c r="F19" s="14" t="n">
+        <f aca="false">SUM(F14:F18)</f>
+        <v>33185.4</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <f aca="false">IFERROR(F19/C19,"")</f>
+        <v>0.358594383151616</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <f aca="false">IF(C19="","",C19-F19)</f>
+        <v>59357.6</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <f aca="false">IFERROR((F19/$B$7)*$B$6,"")</f>
+        <v>73007.88</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <f aca="false">IFERROR(I19/C19,"")</f>
+        <v>0.788907642933555</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16"/>
+      <c r="B20" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="12" t="n">
-        <v>6250</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="13" t="n">
-        <f aca="false">D18+E18</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="14" t="n">
-        <f aca="false">IFERROR(F18/C18,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="13" t="n">
-        <f aca="false">IF(C18="","",C18-F18)</f>
-        <v>6250</v>
-      </c>
-      <c r="I18" s="13" t="n">
-        <f aca="false">IFERROR((F18/$B$7)*$B$6,"")</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="14" t="n">
-        <f aca="false">IFERROR(I18/C18,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11" t="s">
+      <c r="C20" s="18" t="n">
+        <f aca="false">C13+C19</f>
+        <v>346513</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <f aca="false">D13+D19</f>
+        <v>112999.7</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <f aca="false">E13+E19</f>
+        <v>5543</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <f aca="false">F13+F19</f>
+        <v>118542.7</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <f aca="false">IFERROR(F20/C20,"")</f>
+        <v>0.342101739328683</v>
+      </c>
+      <c r="H20" s="18" t="n">
+        <f aca="false">IF(C20="","",C20-F20)</f>
+        <v>227970.3</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <f aca="false">IFERROR((F20/$B$7)*$B$6,"")</f>
+        <v>260793.94</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <f aca="false">IFERROR(I20/C20,"")</f>
+        <v>0.752623826523103</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="21"/>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12" t="n">
-        <v>1276</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="13" t="n">
-        <f aca="false">D19+E19</f>
-        <v>1276</v>
-      </c>
-      <c r="G19" s="14" t="str">
-        <f aca="false">IFERROR(F19/C19,"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="13" t="str">
-        <f aca="false">IF(C19="","",C19-F19)</f>
-        <v/>
-      </c>
-      <c r="I19" s="13" t="n">
-        <f aca="false">IFERROR((F19/$B$7)*$B$6,"")</f>
-        <v>2807.2</v>
-      </c>
-      <c r="J19" s="14" t="str">
-        <f aca="false">IFERROR(I19/C19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18"/>
-      <c r="B20" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="16" t="n">
-        <f aca="false">SUM(C15:C19)</f>
-        <v>92543</v>
-      </c>
-      <c r="D20" s="16" t="n">
-        <f aca="false">SUM(D15:D19)</f>
-        <v>32883.4</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <f aca="false">SUM(E15:E19)</f>
-        <v>302</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <f aca="false">SUM(F15:F19)</f>
-        <v>33185.4</v>
-      </c>
-      <c r="G20" s="17" t="n">
-        <f aca="false">IFERROR(F20/C20,"")</f>
-        <v>0.358594383151616</v>
-      </c>
-      <c r="H20" s="16" t="n">
-        <f aca="false">IF(C20="","",C20-F20)</f>
-        <v>59357.6</v>
-      </c>
-      <c r="I20" s="16" t="n">
-        <f aca="false">IFERROR((F20/$B$7)*$B$6,"")</f>
-        <v>73007.88</v>
-      </c>
-      <c r="J20" s="17" t="n">
-        <f aca="false">IFERROR(I20/C20,"")</f>
-        <v>0.788907642933555</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19"/>
-      <c r="B21" s="20" t="s">
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+    </row>
+    <row r="23" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="21" t="n">
-        <f aca="false">C14+C20</f>
-        <v>346513</v>
-      </c>
-      <c r="D21" s="21" t="n">
-        <f aca="false">D14+D20</f>
-        <v>112999.7</v>
-      </c>
-      <c r="E21" s="21" t="n">
-        <f aca="false">E14+E20</f>
-        <v>5543</v>
-      </c>
-      <c r="F21" s="21" t="n">
-        <f aca="false">F14+F20</f>
-        <v>118542.7</v>
-      </c>
-      <c r="G21" s="22" t="n">
-        <f aca="false">IFERROR(F21/C21,"")</f>
-        <v>0.342101739328683</v>
-      </c>
-      <c r="H21" s="21" t="n">
-        <f aca="false">IF(C21="","",C21-F21)</f>
-        <v>227970.3</v>
-      </c>
-      <c r="I21" s="21" t="n">
-        <f aca="false">IFERROR((F21/$B$7)*$B$6,"")</f>
-        <v>260793.94</v>
-      </c>
-      <c r="J21" s="22" t="n">
-        <f aca="false">IFERROR(I21/C21,"")</f>
+      <c r="B24" s="24" t="n">
+        <f aca="false">B7</f>
+        <v>10</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="25" t="n">
+        <f aca="false">IFERROR(F20/B7,"—")</f>
+        <v>11854.27</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="27" t="n">
+        <f aca="false">J20</f>
         <v>0.752623826523103</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-    </row>
-    <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9" t="s">
+      <c r="C26" s="6"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="29"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9" t="s">
+      <c r="B28" s="31"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-    </row>
-    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="n">
+      <c r="B29" s="24" t="n">
         <f aca="false">IFERROR(B6-B7,"—")</f>
         <v>12</v>
       </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="25" t="n">
-        <f aca="false">IFERROR(H21/(B6-B7),"—")</f>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="25" t="n">
+        <f aca="false">IFERROR(H20/(B6-B7),"—")</f>
         <v>18997.525</v>
       </c>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="26" t="n">
-        <f aca="false">IFERROR((D21+E21)/C21,"—")</f>
-        <v>0.342101739328683</v>
-      </c>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1563,21 +1686,13 @@
     <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="4">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A11:A19"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A10:A18"/>
+    <mergeCell ref="A22:J22"/>
   </mergeCells>
-  <conditionalFormatting sqref="G26">
+  <conditionalFormatting sqref="B26">
     <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0.33</formula>
     </cfRule>
@@ -1635,7 +1750,7 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="32" t="n">
         <v>46250</v>
       </c>
     </row>
@@ -1643,7 +1758,7 @@
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="4" t="n">
         <v>46249</v>
       </c>
     </row>
@@ -1651,7 +1766,7 @@
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="32" t="n">
         <f aca="false">EOMONTH(B3,-1)+1</f>
         <v>46235</v>
       </c>
@@ -1660,7 +1775,7 @@
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="32" t="n">
         <f aca="false">EOMONTH(B3,0)</f>
         <v>46265</v>
       </c>
@@ -1669,7 +1784,7 @@
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="5" t="n">
         <f aca="true">SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B5)))&lt;6)*1)</f>
         <v>22</v>
       </c>
@@ -1678,520 +1793,520 @@
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="5" t="n">
         <f aca="true">SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B3)))&lt;6)*1)</f>
         <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-    </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="D10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="E10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="F10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="G10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="H10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="I10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="J10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="9" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="35" t="n">
         <v>45780</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="35" t="n">
         <v>28518.9</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="35" t="n">
         <v>885</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="11" t="n">
         <f aca="false">D11+E11</f>
         <v>29403.9</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="12" t="n">
         <f aca="false">IFERROR(F11/C11,"")</f>
         <v>0.642287024901704</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="11" t="n">
         <f aca="false">IF(C11="","",C11-F11)</f>
         <v>16376.1</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="I11" s="11" t="n">
         <f aca="false">IFERROR((F11/$B$7)*$B$6,"")</f>
         <v>64688.58</v>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J11" s="12" t="n">
         <f aca="false">IFERROR(I11/C11,"")</f>
         <v>1.41303145478375</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="35" t="n">
         <v>25070</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="35" t="n">
         <v>5330.1</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="35" t="n">
         <v>320</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="11" t="n">
         <f aca="false">D12+E12</f>
         <v>5650.1</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="12" t="n">
         <f aca="false">IFERROR(F12/C12,"")</f>
         <v>0.225372955723973</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="11" t="n">
         <f aca="false">IF(C12="","",C12-F12)</f>
         <v>19419.9</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="I12" s="11" t="n">
         <f aca="false">IFERROR((F12/$B$7)*$B$6,"")</f>
         <v>12430.22</v>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="J12" s="12" t="n">
         <f aca="false">IFERROR(I12/C12,"")</f>
         <v>0.49582050259274</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="A13" s="8"/>
+      <c r="B13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="35" t="n">
         <v>167860</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="35" t="n">
         <v>78350.3</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="13" t="n">
+      <c r="E13" s="36"/>
+      <c r="F13" s="11" t="n">
         <f aca="false">D13+E13</f>
         <v>78350.3</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="12" t="n">
         <f aca="false">IFERROR(F13/C13,"")</f>
         <v>0.466759799833194</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="11" t="n">
         <f aca="false">IF(C13="","",C13-F13)</f>
         <v>89509.7</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="I13" s="11" t="n">
         <f aca="false">IFERROR((F13/$B$7)*$B$6,"")</f>
         <v>172370.66</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="12" t="n">
         <f aca="false">IFERROR(I13/C13,"")</f>
         <v>1.02687155963303</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="A14" s="8"/>
+      <c r="B14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="14" t="n">
         <f aca="false">SUM(C11:C13)</f>
         <v>238710</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="14" t="n">
         <f aca="false">SUM(D11:D13)</f>
         <v>112199.3</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="14" t="n">
         <f aca="false">SUM(E11:E13)</f>
         <v>1205</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="14" t="n">
         <f aca="false">SUM(F11:F13)</f>
         <v>113404.3</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="15" t="n">
         <f aca="false">IFERROR(F14/C14,"")</f>
         <v>0.475071425579155</v>
       </c>
-      <c r="H14" s="16" t="n">
+      <c r="H14" s="14" t="n">
         <f aca="false">IF(C14="","",C14-F14)</f>
         <v>125305.7</v>
       </c>
-      <c r="I14" s="16" t="n">
+      <c r="I14" s="14" t="n">
         <f aca="false">IFERROR((F14/$B$7)*$B$6,"")</f>
         <v>249489.46</v>
       </c>
-      <c r="J14" s="17" t="n">
+      <c r="J14" s="15" t="n">
         <f aca="false">IFERROR(I14/C14,"")</f>
         <v>1.04515713627414</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="35" t="n">
         <v>28992</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="35" t="n">
         <v>8622</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="13" t="n">
+      <c r="E15" s="36"/>
+      <c r="F15" s="11" t="n">
         <f aca="false">D15+E15</f>
         <v>8622</v>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="12" t="n">
         <f aca="false">IFERROR(F15/C15,"")</f>
         <v>0.29739238410596</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="11" t="n">
         <f aca="false">IF(C15="","",C15-F15)</f>
         <v>20370</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I15" s="11" t="n">
         <f aca="false">IFERROR((F15/$B$7)*$B$6,"")</f>
         <v>18968.4</v>
       </c>
-      <c r="J15" s="14" t="n">
+      <c r="J15" s="12" t="n">
         <f aca="false">IFERROR(I15/C15,"")</f>
         <v>0.654263245033113</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="12" t="n">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="13" t="n">
+      <c r="E16" s="36"/>
+      <c r="F16" s="11" t="n">
         <f aca="false">D16+E16</f>
         <v>0</v>
       </c>
-      <c r="G16" s="14" t="str">
+      <c r="G16" s="12" t="str">
         <f aca="false">IFERROR(F16/C16,"")</f>
         <v/>
       </c>
-      <c r="H16" s="13" t="str">
+      <c r="H16" s="11" t="str">
         <f aca="false">IF(C16="","",C16-F16)</f>
         <v/>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="I16" s="11" t="n">
         <f aca="false">IFERROR((F16/$B$7)*$B$6,"")</f>
         <v>0</v>
       </c>
-      <c r="J16" s="14" t="str">
+      <c r="J16" s="12" t="str">
         <f aca="false">IFERROR(I16/C16,"")</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="12" t="n">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="35" t="n">
         <v>43600</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="35" t="n">
         <v>27849.1</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="35" t="n">
         <v>2240</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="11" t="n">
         <f aca="false">D17+E17</f>
         <v>30089.1</v>
       </c>
-      <c r="G17" s="14" t="n">
+      <c r="G17" s="12" t="n">
         <f aca="false">IFERROR(F17/C17,"")</f>
         <v>0.690116972477064</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="11" t="n">
         <f aca="false">IF(C17="","",C17-F17)</f>
         <v>13510.9</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="I17" s="11" t="n">
         <f aca="false">IFERROR((F17/$B$7)*$B$6,"")</f>
         <v>66196.02</v>
       </c>
-      <c r="J17" s="14" t="n">
+      <c r="J17" s="12" t="n">
         <f aca="false">IFERROR(I17/C17,"")</f>
         <v>1.51825733944954</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="12" t="n">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="35" t="n">
         <v>6250</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="13" t="n">
+      <c r="E18" s="36"/>
+      <c r="F18" s="11" t="n">
         <f aca="false">D18+E18</f>
         <v>0</v>
       </c>
-      <c r="G18" s="14" t="n">
+      <c r="G18" s="12" t="n">
         <f aca="false">IFERROR(F18/C18,"")</f>
         <v>0</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="H18" s="11" t="n">
         <f aca="false">IF(C18="","",C18-F18)</f>
         <v>6250</v>
       </c>
-      <c r="I18" s="13" t="n">
+      <c r="I18" s="11" t="n">
         <f aca="false">IFERROR((F18/$B$7)*$B$6,"")</f>
         <v>0</v>
       </c>
-      <c r="J18" s="14" t="n">
+      <c r="J18" s="12" t="n">
         <f aca="false">IFERROR(I18/C18,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="12" t="n">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="35" t="n">
         <v>457</v>
       </c>
-      <c r="E19" s="29"/>
-      <c r="F19" s="13" t="n">
+      <c r="E19" s="36"/>
+      <c r="F19" s="11" t="n">
         <f aca="false">D19+E19</f>
         <v>457</v>
       </c>
-      <c r="G19" s="14" t="str">
+      <c r="G19" s="12" t="str">
         <f aca="false">IFERROR(F19/C19,"")</f>
         <v/>
       </c>
-      <c r="H19" s="13" t="str">
+      <c r="H19" s="11" t="str">
         <f aca="false">IF(C19="","",C19-F19)</f>
         <v/>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="I19" s="11" t="n">
         <f aca="false">IFERROR((F19/$B$7)*$B$6,"")</f>
         <v>1005.4</v>
       </c>
-      <c r="J19" s="14" t="str">
+      <c r="J19" s="12" t="str">
         <f aca="false">IFERROR(I19/C19,"")</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18"/>
-      <c r="B20" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="A20" s="16"/>
+      <c r="B20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="14" t="n">
         <f aca="false">SUM(C15:C19)</f>
         <v>78842</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="14" t="n">
         <f aca="false">SUM(D15:D19)</f>
         <v>36928.1</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="14" t="n">
         <f aca="false">SUM(E15:E19)</f>
         <v>2240</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="14" t="n">
         <f aca="false">SUM(F15:F19)</f>
         <v>39168.1</v>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="G20" s="15" t="n">
         <f aca="false">IFERROR(F20/C20,"")</f>
         <v>0.496792318814845</v>
       </c>
-      <c r="H20" s="16" t="n">
+      <c r="H20" s="14" t="n">
         <f aca="false">IF(C20="","",C20-F20)</f>
         <v>39673.9</v>
       </c>
-      <c r="I20" s="16" t="n">
+      <c r="I20" s="14" t="n">
         <f aca="false">IFERROR((F20/$B$7)*$B$6,"")</f>
         <v>86169.82</v>
       </c>
-      <c r="J20" s="17" t="n">
+      <c r="J20" s="15" t="n">
         <f aca="false">IFERROR(I20/C20,"")</f>
         <v>1.09294310139266</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19"/>
-      <c r="B21" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="21" t="n">
+      <c r="A21" s="37"/>
+      <c r="B21" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="18" t="n">
         <f aca="false">C14+C20</f>
         <v>317552</v>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="18" t="n">
         <f aca="false">D14+D20</f>
         <v>149127.4</v>
       </c>
-      <c r="E21" s="21" t="n">
+      <c r="E21" s="18" t="n">
         <f aca="false">E14+E20</f>
         <v>3445</v>
       </c>
-      <c r="F21" s="21" t="n">
+      <c r="F21" s="18" t="n">
         <f aca="false">F14+F20</f>
         <v>152572.4</v>
       </c>
-      <c r="G21" s="22" t="n">
+      <c r="G21" s="19" t="n">
         <f aca="false">IFERROR(F21/C21,"")</f>
         <v>0.480464301909609</v>
       </c>
-      <c r="H21" s="21" t="n">
+      <c r="H21" s="18" t="n">
         <f aca="false">IF(C21="","",C21-F21)</f>
         <v>164979.6</v>
       </c>
-      <c r="I21" s="21" t="n">
+      <c r="I21" s="18" t="n">
         <f aca="false">IFERROR((F21/$B$7)*$B$6,"")</f>
         <v>335659.28</v>
       </c>
-      <c r="J21" s="22" t="n">
+      <c r="J21" s="19" t="n">
         <f aca="false">IFERROR(I21/C21,"")</f>
         <v>1.05702146420114</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
+      <c r="A23" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="A25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="n">
+      <c r="A26" s="38" t="n">
         <f aca="false">IFERROR(B6-B7,"—")</f>
         <v>12</v>
       </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="25" t="n">
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="39" t="n">
         <f aca="false">IFERROR(H21/(B6-B7),"—")</f>
         <v>13748.3</v>
       </c>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="26" t="n">
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="40" t="n">
         <f aca="false">IFERROR((D21+E21)/C21,"—")</f>
         <v>0.480464301909609</v>
       </c>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="40"/>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
+      <c r="A28" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2250,7 +2365,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2266,7 +2381,7 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="32" t="n">
         <v>46250</v>
       </c>
     </row>
@@ -2274,7 +2389,7 @@
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="4" t="n">
         <v>46249</v>
       </c>
     </row>
@@ -2282,7 +2397,7 @@
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="32" t="n">
         <f aca="false">EOMONTH(B3,-1)+1</f>
         <v>46235</v>
       </c>
@@ -2291,7 +2406,7 @@
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="32" t="n">
         <f aca="false">EOMONTH(B3,0)</f>
         <v>46265</v>
       </c>
@@ -2300,7 +2415,7 @@
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="5" t="n">
         <f aca="true">SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B5)))&lt;6)*1)</f>
         <v>22</v>
       </c>
@@ -2309,520 +2424,520 @@
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="5" t="n">
         <f aca="true">SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B3)))&lt;6)*1)</f>
         <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
+      <c r="A8" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-    </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="D10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="E10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="F10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="G10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="H10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="I10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="J10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="9" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="35" t="n">
         <v>30520</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="35" t="n">
         <v>13592.7</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="35" t="n">
         <v>75</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="11" t="n">
         <f aca="false">D11+E11</f>
         <v>13667.7</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="12" t="n">
         <f aca="false">IFERROR(F11/C11,"")</f>
         <v>0.447827653997379</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="11" t="n">
         <f aca="false">IF(C11="","",C11-F11)</f>
         <v>16852.3</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="I11" s="11" t="n">
         <f aca="false">IFERROR((F11/$B$7)*$B$6,"")</f>
         <v>30068.94</v>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J11" s="12" t="n">
         <f aca="false">IFERROR(I11/C11,"")</f>
         <v>0.985220838794233</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="35" t="n">
         <v>30520</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="35" t="n">
         <v>9861.2</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="35" t="n">
         <v>408</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="11" t="n">
         <f aca="false">D12+E12</f>
         <v>10269.2</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="12" t="n">
         <f aca="false">IFERROR(F12/C12,"")</f>
         <v>0.336474442988205</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="11" t="n">
         <f aca="false">IF(C12="","",C12-F12)</f>
         <v>20250.8</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="I12" s="11" t="n">
         <f aca="false">IFERROR((F12/$B$7)*$B$6,"")</f>
         <v>22592.24</v>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="J12" s="12" t="n">
         <f aca="false">IFERROR(I12/C12,"")</f>
         <v>0.74024377457405</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="A13" s="8"/>
+      <c r="B13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="35" t="n">
         <v>161865</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="35" t="n">
         <v>64049.2</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="13" t="n">
+      <c r="E13" s="36"/>
+      <c r="F13" s="11" t="n">
         <f aca="false">D13+E13</f>
         <v>64049.2</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="12" t="n">
         <f aca="false">IFERROR(F13/C13,"")</f>
         <v>0.395695178080499</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="11" t="n">
         <f aca="false">IF(C13="","",C13-F13)</f>
         <v>97815.8</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="I13" s="11" t="n">
         <f aca="false">IFERROR((F13/$B$7)*$B$6,"")</f>
         <v>140908.24</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="12" t="n">
         <f aca="false">IFERROR(I13/C13,"")</f>
         <v>0.870529391777098</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="A14" s="8"/>
+      <c r="B14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="14" t="n">
         <f aca="false">SUM(C11:C13)</f>
         <v>222905</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="14" t="n">
         <f aca="false">SUM(D11:D13)</f>
         <v>87503.1</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="14" t="n">
         <f aca="false">SUM(E11:E13)</f>
         <v>483</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="14" t="n">
         <f aca="false">SUM(F11:F13)</f>
         <v>87986.1</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="15" t="n">
         <f aca="false">IFERROR(F14/C14,"")</f>
         <v>0.394724658486799</v>
       </c>
-      <c r="H14" s="16" t="n">
+      <c r="H14" s="14" t="n">
         <f aca="false">IF(C14="","",C14-F14)</f>
         <v>134918.9</v>
       </c>
-      <c r="I14" s="16" t="n">
+      <c r="I14" s="14" t="n">
         <f aca="false">IFERROR((F14/$B$7)*$B$6,"")</f>
         <v>193569.42</v>
       </c>
-      <c r="J14" s="17" t="n">
+      <c r="J14" s="15" t="n">
         <f aca="false">IFERROR(I14/C14,"")</f>
         <v>0.868394248670959</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="35" t="n">
         <v>12794</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="35" t="n">
         <v>4269</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="13" t="n">
+      <c r="E15" s="36"/>
+      <c r="F15" s="11" t="n">
         <f aca="false">D15+E15</f>
         <v>4269</v>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="12" t="n">
         <f aca="false">IFERROR(F15/C15,"")</f>
         <v>0.333672033765828</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="11" t="n">
         <f aca="false">IF(C15="","",C15-F15)</f>
         <v>8525</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I15" s="11" t="n">
         <f aca="false">IFERROR((F15/$B$7)*$B$6,"")</f>
         <v>9391.8</v>
       </c>
-      <c r="J15" s="14" t="n">
+      <c r="J15" s="12" t="n">
         <f aca="false">IFERROR(I15/C15,"")</f>
         <v>0.734078474284821</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="13" t="n">
+      <c r="E16" s="36"/>
+      <c r="F16" s="11" t="n">
         <f aca="false">D16+E16</f>
         <v>0</v>
       </c>
-      <c r="G16" s="14" t="str">
+      <c r="G16" s="12" t="str">
         <f aca="false">IFERROR(F16/C16,"")</f>
         <v/>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="11" t="n">
         <f aca="false">IF(C16="","",C16-F16)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="I16" s="11" t="n">
         <f aca="false">IFERROR((F16/$B$7)*$B$6,"")</f>
         <v>0</v>
       </c>
-      <c r="J16" s="14" t="str">
+      <c r="J16" s="12" t="str">
         <f aca="false">IFERROR(I16/C16,"")</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="12" t="n">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="35" t="n">
         <v>6625</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="35" t="n">
         <v>4045</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="35" t="n">
         <v>537</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="11" t="n">
         <f aca="false">D17+E17</f>
         <v>4582</v>
       </c>
-      <c r="G17" s="14" t="n">
+      <c r="G17" s="12" t="n">
         <f aca="false">IFERROR(F17/C17,"")</f>
         <v>0.691622641509434</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="11" t="n">
         <f aca="false">IF(C17="","",C17-F17)</f>
         <v>2043</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="I17" s="11" t="n">
         <f aca="false">IFERROR((F17/$B$7)*$B$6,"")</f>
         <v>10080.4</v>
       </c>
-      <c r="J17" s="14" t="n">
+      <c r="J17" s="12" t="n">
         <f aca="false">IFERROR(I17/C17,"")</f>
         <v>1.52156981132075</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="12" t="n">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="35" t="n">
         <v>22036</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="35" t="n">
         <v>1212</v>
       </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="13" t="n">
+      <c r="E18" s="36"/>
+      <c r="F18" s="11" t="n">
         <f aca="false">D18+E18</f>
         <v>1212</v>
       </c>
-      <c r="G18" s="14" t="n">
+      <c r="G18" s="12" t="n">
         <f aca="false">IFERROR(F18/C18,"")</f>
         <v>0.0550009076057361</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="H18" s="11" t="n">
         <f aca="false">IF(C18="","",C18-F18)</f>
         <v>20824</v>
       </c>
-      <c r="I18" s="13" t="n">
+      <c r="I18" s="11" t="n">
         <f aca="false">IFERROR((F18/$B$7)*$B$6,"")</f>
         <v>2666.4</v>
       </c>
-      <c r="J18" s="14" t="n">
+      <c r="J18" s="12" t="n">
         <f aca="false">IFERROR(I18/C18,"")</f>
         <v>0.121001996732619</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="13" t="n">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="11" t="n">
         <f aca="false">D19+E19</f>
         <v>0</v>
       </c>
-      <c r="G19" s="14" t="str">
+      <c r="G19" s="12" t="str">
         <f aca="false">IFERROR(F19/C19,"")</f>
         <v/>
       </c>
-      <c r="H19" s="13" t="str">
+      <c r="H19" s="11" t="str">
         <f aca="false">IF(C19="","",C19-F19)</f>
         <v/>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="I19" s="11" t="n">
         <f aca="false">IFERROR((F19/$B$7)*$B$6,"")</f>
         <v>0</v>
       </c>
-      <c r="J19" s="14" t="str">
+      <c r="J19" s="12" t="str">
         <f aca="false">IFERROR(I19/C19,"")</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18"/>
-      <c r="B20" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="A20" s="16"/>
+      <c r="B20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="14" t="n">
         <f aca="false">SUM(C15:C19)</f>
         <v>41455</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="14" t="n">
         <f aca="false">SUM(D15:D19)</f>
         <v>9526</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="14" t="n">
         <f aca="false">SUM(E15:E19)</f>
         <v>537</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="14" t="n">
         <f aca="false">SUM(F15:F19)</f>
         <v>10063</v>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="G20" s="15" t="n">
         <f aca="false">IFERROR(F20/C20,"")</f>
         <v>0.242745145338319</v>
       </c>
-      <c r="H20" s="16" t="n">
+      <c r="H20" s="14" t="n">
         <f aca="false">IF(C20="","",C20-F20)</f>
         <v>31392</v>
       </c>
-      <c r="I20" s="16" t="n">
+      <c r="I20" s="14" t="n">
         <f aca="false">IFERROR((F20/$B$7)*$B$6,"")</f>
         <v>22138.6</v>
       </c>
-      <c r="J20" s="17" t="n">
+      <c r="J20" s="15" t="n">
         <f aca="false">IFERROR(I20/C20,"")</f>
         <v>0.534039319744301</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19"/>
-      <c r="B21" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="21" t="n">
+      <c r="A21" s="37"/>
+      <c r="B21" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="18" t="n">
         <f aca="false">C14+C20</f>
         <v>264360</v>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="18" t="n">
         <f aca="false">D14+D20</f>
         <v>97029.1</v>
       </c>
-      <c r="E21" s="21" t="n">
+      <c r="E21" s="18" t="n">
         <f aca="false">E14+E20</f>
         <v>1020</v>
       </c>
-      <c r="F21" s="21" t="n">
+      <c r="F21" s="18" t="n">
         <f aca="false">F14+F20</f>
         <v>98049.1</v>
       </c>
-      <c r="G21" s="22" t="n">
+      <c r="G21" s="19" t="n">
         <f aca="false">IFERROR(F21/C21,"")</f>
         <v>0.370892343773642</v>
       </c>
-      <c r="H21" s="21" t="n">
+      <c r="H21" s="18" t="n">
         <f aca="false">IF(C21="","",C21-F21)</f>
         <v>166310.9</v>
       </c>
-      <c r="I21" s="21" t="n">
+      <c r="I21" s="18" t="n">
         <f aca="false">IFERROR((F21/$B$7)*$B$6,"")</f>
         <v>215708.02</v>
       </c>
-      <c r="J21" s="22" t="n">
+      <c r="J21" s="19" t="n">
         <f aca="false">IFERROR(I21/C21,"")</f>
         <v>0.815963156302012</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
+      <c r="A23" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="A25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="n">
+      <c r="A26" s="38" t="n">
         <f aca="false">IFERROR(B6-B7,"—")</f>
         <v>12</v>
       </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="25" t="n">
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="39" t="n">
         <f aca="false">IFERROR(H21/(B6-B7),"—")</f>
         <v>13859.2416666667</v>
       </c>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="26" t="n">
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="40" t="n">
         <f aca="false">IFERROR((D21+E21)/C21,"—")</f>
         <v>0.370892343773642</v>
       </c>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="40"/>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
+      <c r="A28" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2881,7 +2996,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2897,7 +3012,7 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="32" t="n">
         <v>46250</v>
       </c>
     </row>
@@ -2905,7 +3020,7 @@
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="4" t="n">
         <v>46249</v>
       </c>
     </row>
@@ -2913,7 +3028,7 @@
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="32" t="n">
         <f aca="false">EOMONTH(B3,-1)+1</f>
         <v>46235</v>
       </c>
@@ -2922,7 +3037,7 @@
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="32" t="n">
         <f aca="false">EOMONTH(B3,0)</f>
         <v>46265</v>
       </c>
@@ -2931,7 +3046,7 @@
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="5" t="n">
         <f aca="true">SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B5)))&lt;6)*1)</f>
         <v>22</v>
       </c>
@@ -2940,520 +3055,520 @@
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="5" t="n">
         <f aca="true">SUMPRODUCT((WEEKDAY(ROW(INDIRECT(B4&amp;":"&amp;B3)))&lt;6)*1)</f>
         <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
+      <c r="A8" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-    </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="D10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="E10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="F10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="G10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="H10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="I10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="J10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="9" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="35" t="n">
         <v>32700</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="35" t="n">
         <v>10036.8</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="11" t="n">
         <f aca="false">D11+E11</f>
         <v>10036.8</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="12" t="n">
         <f aca="false">IFERROR(F11/C11,"")</f>
         <v>0.306935779816514</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="11" t="n">
         <f aca="false">IF(C11="","",C11-F11)</f>
         <v>22663.2</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="I11" s="11" t="n">
         <f aca="false">IFERROR((F11/$B$7)*$B$6,"")</f>
         <v>22080.96</v>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J11" s="12" t="n">
         <f aca="false">IFERROR(I11/C11,"")</f>
         <v>0.67525871559633</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="35" t="n">
         <v>28340</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="35" t="n">
         <v>11639.9</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="35" t="n">
         <v>481</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="11" t="n">
         <f aca="false">D12+E12</f>
         <v>12120.9</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="12" t="n">
         <f aca="false">IFERROR(F12/C12,"")</f>
         <v>0.427695836273818</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="11" t="n">
         <f aca="false">IF(C12="","",C12-F12)</f>
         <v>16219.1</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="I12" s="11" t="n">
         <f aca="false">IFERROR((F12/$B$7)*$B$6,"")</f>
         <v>26665.98</v>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="J12" s="12" t="n">
         <f aca="false">IFERROR(I12/C12,"")</f>
         <v>0.940930839802399</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="A13" s="8"/>
+      <c r="B13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="35" t="n">
         <v>149875</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="35" t="n">
         <v>56289.2</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="13" t="n">
+      <c r="E13" s="36"/>
+      <c r="F13" s="11" t="n">
         <f aca="false">D13+E13</f>
         <v>56289.2</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="12" t="n">
         <f aca="false">IFERROR(F13/C13,"")</f>
         <v>0.375574311926606</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="11" t="n">
         <f aca="false">IF(C13="","",C13-F13)</f>
         <v>93585.8</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="I13" s="11" t="n">
         <f aca="false">IFERROR((F13/$B$7)*$B$6,"")</f>
         <v>123836.24</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="12" t="n">
         <f aca="false">IFERROR(I13/C13,"")</f>
         <v>0.826263486238532</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="A14" s="8"/>
+      <c r="B14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="14" t="n">
         <f aca="false">SUM(C11:C13)</f>
         <v>210915</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="14" t="n">
         <f aca="false">SUM(D11:D13)</f>
         <v>77965.9</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="14" t="n">
         <f aca="false">SUM(E11:E13)</f>
         <v>481</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="14" t="n">
         <f aca="false">SUM(F11:F13)</f>
         <v>78446.9</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="15" t="n">
         <f aca="false">IFERROR(F14/C14,"")</f>
         <v>0.371936087997535</v>
       </c>
-      <c r="H14" s="16" t="n">
+      <c r="H14" s="14" t="n">
         <f aca="false">IF(C14="","",C14-F14)</f>
         <v>132468.1</v>
       </c>
-      <c r="I14" s="16" t="n">
+      <c r="I14" s="14" t="n">
         <f aca="false">IFERROR((F14/$B$7)*$B$6,"")</f>
         <v>172583.18</v>
       </c>
-      <c r="J14" s="17" t="n">
+      <c r="J14" s="15" t="n">
         <f aca="false">IFERROR(I14/C14,"")</f>
         <v>0.818259393594576</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="35" t="n">
         <v>10756</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="35" t="n">
         <v>1222</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="13" t="n">
+      <c r="E15" s="36"/>
+      <c r="F15" s="11" t="n">
         <f aca="false">D15+E15</f>
         <v>1222</v>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="12" t="n">
         <f aca="false">IFERROR(F15/C15,"")</f>
         <v>0.113611007809595</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="11" t="n">
         <f aca="false">IF(C15="","",C15-F15)</f>
         <v>9534</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I15" s="11" t="n">
         <f aca="false">IFERROR((F15/$B$7)*$B$6,"")</f>
         <v>2688.4</v>
       </c>
-      <c r="J15" s="14" t="n">
+      <c r="J15" s="12" t="n">
         <f aca="false">IFERROR(I15/C15,"")</f>
         <v>0.249944217181108</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="35" t="n">
         <v>7964</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="35" t="n">
         <v>899</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="13" t="n">
+      <c r="E16" s="36"/>
+      <c r="F16" s="11" t="n">
         <f aca="false">D16+E16</f>
         <v>899</v>
       </c>
-      <c r="G16" s="14" t="n">
+      <c r="G16" s="12" t="n">
         <f aca="false">IFERROR(F16/C16,"")</f>
         <v>0.112882973380211</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="11" t="n">
         <f aca="false">IF(C16="","",C16-F16)</f>
         <v>7065</v>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="I16" s="11" t="n">
         <f aca="false">IFERROR((F16/$B$7)*$B$6,"")</f>
         <v>1977.8</v>
       </c>
-      <c r="J16" s="14" t="n">
+      <c r="J16" s="12" t="n">
         <f aca="false">IFERROR(I16/C16,"")</f>
         <v>0.248342541436464</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="12" t="n">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="35" t="n">
         <v>21564</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="35" t="n">
         <v>7584.6</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="35" t="n">
         <v>132</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="11" t="n">
         <f aca="false">D17+E17</f>
         <v>7716.6</v>
       </c>
-      <c r="G17" s="14" t="n">
+      <c r="G17" s="12" t="n">
         <f aca="false">IFERROR(F17/C17,"")</f>
         <v>0.357846410684474</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="11" t="n">
         <f aca="false">IF(C17="","",C17-F17)</f>
         <v>13847.4</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="I17" s="11" t="n">
         <f aca="false">IFERROR((F17/$B$7)*$B$6,"")</f>
         <v>16976.52</v>
       </c>
-      <c r="J17" s="14" t="n">
+      <c r="J17" s="12" t="n">
         <f aca="false">IFERROR(I17/C17,"")</f>
         <v>0.787262103505843</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="12" t="n">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="35" t="n">
         <v>5875</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="35" t="n">
         <v>157</v>
       </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="13" t="n">
+      <c r="E18" s="36"/>
+      <c r="F18" s="11" t="n">
         <f aca="false">D18+E18</f>
         <v>157</v>
       </c>
-      <c r="G18" s="14" t="n">
+      <c r="G18" s="12" t="n">
         <f aca="false">IFERROR(F18/C18,"")</f>
         <v>0.0267234042553192</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="H18" s="11" t="n">
         <f aca="false">IF(C18="","",C18-F18)</f>
         <v>5718</v>
       </c>
-      <c r="I18" s="13" t="n">
+      <c r="I18" s="11" t="n">
         <f aca="false">IFERROR((F18/$B$7)*$B$6,"")</f>
         <v>345.4</v>
       </c>
-      <c r="J18" s="14" t="n">
+      <c r="J18" s="12" t="n">
         <f aca="false">IFERROR(I18/C18,"")</f>
         <v>0.0587914893617021</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="13" t="n">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="11" t="n">
         <f aca="false">D19+E19</f>
         <v>0</v>
       </c>
-      <c r="G19" s="14" t="str">
+      <c r="G19" s="12" t="str">
         <f aca="false">IFERROR(F19/C19,"")</f>
         <v/>
       </c>
-      <c r="H19" s="13" t="str">
+      <c r="H19" s="11" t="str">
         <f aca="false">IF(C19="","",C19-F19)</f>
         <v/>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="I19" s="11" t="n">
         <f aca="false">IFERROR((F19/$B$7)*$B$6,"")</f>
         <v>0</v>
       </c>
-      <c r="J19" s="14" t="str">
+      <c r="J19" s="12" t="str">
         <f aca="false">IFERROR(I19/C19,"")</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18"/>
-      <c r="B20" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="A20" s="16"/>
+      <c r="B20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="14" t="n">
         <f aca="false">SUM(C15:C19)</f>
         <v>46159</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="14" t="n">
         <f aca="false">SUM(D15:D19)</f>
         <v>9862.6</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="14" t="n">
         <f aca="false">SUM(E15:E19)</f>
         <v>132</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="14" t="n">
         <f aca="false">SUM(F15:F19)</f>
         <v>9994.6</v>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="G20" s="15" t="n">
         <f aca="false">IFERROR(F20/C20,"")</f>
         <v>0.216525487987175</v>
       </c>
-      <c r="H20" s="16" t="n">
+      <c r="H20" s="14" t="n">
         <f aca="false">IF(C20="","",C20-F20)</f>
         <v>36164.4</v>
       </c>
-      <c r="I20" s="16" t="n">
+      <c r="I20" s="14" t="n">
         <f aca="false">IFERROR((F20/$B$7)*$B$6,"")</f>
         <v>21988.12</v>
       </c>
-      <c r="J20" s="17" t="n">
+      <c r="J20" s="15" t="n">
         <f aca="false">IFERROR(I20/C20,"")</f>
         <v>0.476356073571785</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19"/>
-      <c r="B21" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="21" t="n">
+      <c r="A21" s="37"/>
+      <c r="B21" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="18" t="n">
         <f aca="false">C14+C20</f>
         <v>257074</v>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="18" t="n">
         <f aca="false">D14+D20</f>
         <v>87828.5</v>
       </c>
-      <c r="E21" s="21" t="n">
+      <c r="E21" s="18" t="n">
         <f aca="false">E14+E20</f>
         <v>613</v>
       </c>
-      <c r="F21" s="21" t="n">
+      <c r="F21" s="18" t="n">
         <f aca="false">F14+F20</f>
         <v>88441.5</v>
       </c>
-      <c r="G21" s="22" t="n">
+      <c r="G21" s="19" t="n">
         <f aca="false">IFERROR(F21/C21,"")</f>
         <v>0.34403129060115</v>
       </c>
-      <c r="H21" s="21" t="n">
+      <c r="H21" s="18" t="n">
         <f aca="false">IF(C21="","",C21-F21)</f>
         <v>168632.5</v>
       </c>
-      <c r="I21" s="21" t="n">
+      <c r="I21" s="18" t="n">
         <f aca="false">IFERROR((F21/$B$7)*$B$6,"")</f>
         <v>194571.3</v>
       </c>
-      <c r="J21" s="22" t="n">
+      <c r="J21" s="19" t="n">
         <f aca="false">IFERROR(I21/C21,"")</f>
         <v>0.75686883932253</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
+      <c r="A23" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="A25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="n">
+      <c r="A26" s="38" t="n">
         <f aca="false">IFERROR(B6-B7,"—")</f>
         <v>12</v>
       </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="25" t="n">
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="39" t="n">
         <f aca="false">IFERROR(H21/(B6-B7),"—")</f>
         <v>14052.7083333333</v>
       </c>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="26" t="n">
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="40" t="n">
         <f aca="false">IFERROR((D21+E21)/C21,"—")</f>
         <v>0.34403129060115</v>
       </c>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="40"/>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
+      <c r="A28" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3507,221 +3622,221 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="A1" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="32" t="str">
+      <c r="A2" s="43" t="str">
         <f aca="false">"תצוגת מרכז לכל הסוכנים — נכון לתאריך חישוב "&amp;TEXT(חאזם!B2,"dd/mm/yy")&amp;" | יום בדיקה: "&amp;TEXT(חאזם!B3,"dd/mm/yy")&amp;"  |  סך ימי א-ה בחודש: "&amp;חאזם!B6&amp;"  |  ימים שעברו: "&amp;חאזם!B7&amp;"  |  ימים שנותרו: "&amp;חאזם!A26</f>
-        <v>תצוגת מרכז לכל הסוכנים — נכון לתאריך חישוב 16/08/26 | יום בדיקה: 15/08/26  |  סך ימי א-ה בחודש: 22  |  ימים שעברו: 10  |  ימים שנותרו: 12</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
+        <v>תצוגת מרכז לכל הסוכנים — נכון לתאריך חישוב 16/08/26 | יום בדיקה: 15/08/26  |  סך ימי א-ה בחודש: 22  |  ימים שעברו: 10  |  ימים שנותרו: קצב (%)</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
     </row>
     <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
+      <c r="A3" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="34" t="s">
-        <v>52</v>
+      <c r="C5" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="35" t="str">
+      <c r="A6" s="46" t="n">
         <f aca="false">חאזם!A11</f>
-        <v>חאזם</v>
-      </c>
-      <c r="B6" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" s="47" t="n">
         <f aca="false">חאזם!C21</f>
-        <v>346513</v>
-      </c>
-      <c r="C6" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="47" t="n">
         <f aca="false">חאזם!D21+חאזם!E21</f>
-        <v>118542.7</v>
-      </c>
-      <c r="D6" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="48" t="n">
         <f aca="false">חאזם!G21</f>
-        <v>0.342101739328683</v>
-      </c>
-      <c r="E6" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="48" t="n">
         <f aca="false">חאזם!J21</f>
-        <v>0.752623826523103</v>
-      </c>
-      <c r="F6" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="49" t="str">
         <f aca="false">חאזם!A26</f>
-        <v>12</v>
-      </c>
-      <c r="G6" s="36" t="n">
+        <v>קצב (%)</v>
+      </c>
+      <c r="G6" s="47" t="n">
         <f aca="false">חאזם!D26</f>
-        <v>18997.525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="35" t="str">
+      <c r="A7" s="46" t="str">
         <f aca="false">דודו!A11</f>
         <v>דודו</v>
       </c>
-      <c r="B7" s="36" t="n">
+      <c r="B7" s="47" t="n">
         <f aca="false">דודו!C21</f>
         <v>317552</v>
       </c>
-      <c r="C7" s="36" t="n">
+      <c r="C7" s="47" t="n">
         <f aca="false">דודו!D21+דודו!E21</f>
         <v>152572.4</v>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="48" t="n">
         <f aca="false">דודו!G21</f>
         <v>0.480464301909609</v>
       </c>
-      <c r="E7" s="37" t="n">
+      <c r="E7" s="48" t="n">
         <f aca="false">דודו!J21</f>
         <v>1.05702146420114</v>
       </c>
-      <c r="F7" s="38" t="n">
+      <c r="F7" s="49" t="n">
         <f aca="false">דודו!A26</f>
         <v>12</v>
       </c>
-      <c r="G7" s="36" t="n">
+      <c r="G7" s="47" t="n">
         <f aca="false">דודו!D26</f>
         <v>13748.3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="35" t="str">
+      <c r="A8" s="46" t="str">
         <f aca="false">חיים!A11</f>
         <v>חיים</v>
       </c>
-      <c r="B8" s="36" t="n">
+      <c r="B8" s="47" t="n">
         <f aca="false">חיים!C21</f>
         <v>264360</v>
       </c>
-      <c r="C8" s="36" t="n">
+      <c r="C8" s="47" t="n">
         <f aca="false">חיים!D21+חיים!E21</f>
         <v>98049.1</v>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="48" t="n">
         <f aca="false">חיים!G21</f>
         <v>0.370892343773642</v>
       </c>
-      <c r="E8" s="37" t="n">
+      <c r="E8" s="48" t="n">
         <f aca="false">חיים!J21</f>
         <v>0.815963156302012</v>
       </c>
-      <c r="F8" s="38" t="n">
+      <c r="F8" s="49" t="n">
         <f aca="false">חיים!A26</f>
         <v>12</v>
       </c>
-      <c r="G8" s="36" t="n">
+      <c r="G8" s="47" t="n">
         <f aca="false">חיים!D26</f>
         <v>13859.2416666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="35" t="str">
+      <c r="A9" s="46" t="str">
         <f aca="false">סטאס!A11</f>
         <v>סטאס</v>
       </c>
-      <c r="B9" s="36" t="n">
+      <c r="B9" s="47" t="n">
         <f aca="false">סטאס!C21</f>
         <v>257074</v>
       </c>
-      <c r="C9" s="36" t="n">
+      <c r="C9" s="47" t="n">
         <f aca="false">סטאס!D21+סטאס!E21</f>
         <v>88441.5</v>
       </c>
-      <c r="D9" s="37" t="n">
+      <c r="D9" s="48" t="n">
         <f aca="false">סטאס!G21</f>
         <v>0.34403129060115</v>
       </c>
-      <c r="E9" s="37" t="n">
+      <c r="E9" s="48" t="n">
         <f aca="false">סטאס!J21</f>
         <v>0.75686883932253</v>
       </c>
-      <c r="F9" s="38" t="n">
+      <c r="F9" s="49" t="n">
         <f aca="false">סטאס!A26</f>
         <v>12</v>
       </c>
-      <c r="G9" s="36" t="n">
+      <c r="G9" s="47" t="n">
         <f aca="false">סטאס!D26</f>
         <v>14052.7083333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="40" t="n">
+      <c r="A10" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="51" t="n">
         <f aca="false">SUM(B6:B9)</f>
-        <v>1185499</v>
-      </c>
-      <c r="C10" s="40" t="n">
+        <v>838986</v>
+      </c>
+      <c r="C10" s="51" t="n">
         <f aca="false">SUM(C6:C9)</f>
-        <v>457605.7</v>
-      </c>
-      <c r="D10" s="41" t="n">
+        <v>339063</v>
+      </c>
+      <c r="D10" s="52" t="n">
         <f aca="false">IFERROR(C10/B10,"")</f>
-        <v>0.386002603123242</v>
-      </c>
-      <c r="E10" s="41" t="n">
+        <v>0.404134276376483</v>
+      </c>
+      <c r="E10" s="52" t="n">
         <f aca="false">IFERROR((חאזם!I21+דודו!I21+חיים!I21+סטאס!I21)/B10,"")</f>
-        <v>0.849205726871132</v>
-      </c>
-      <c r="F10" s="42" t="n">
+        <v>0.889095408028263</v>
+      </c>
+      <c r="F10" s="53" t="str">
         <f aca="false">F6</f>
-        <v>12</v>
-      </c>
-      <c r="G10" s="40" t="n">
+        <v>קצב (%)</v>
+      </c>
+      <c r="G10" s="51" t="str">
         <f aca="false">IFERROR((B10-C10)/F10,"")</f>
-        <v>60657.775</v>
+        <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
+      <c r="A12" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/kirill/outputs/hazam-tracking-dashboard.xlsx
+++ b/kirill/outputs/hazam-tracking-dashboard.xlsx
@@ -535,10 +535,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -616,6 +612,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1467,6 +1467,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13"/>
       <c r="B19" s="13" t="s">
         <v>21</v>
       </c>
@@ -1505,38 +1506,38 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16"/>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="18" t="n">
+      <c r="C20" s="17" t="n">
         <f aca="false">C13+C19</f>
         <v>346513</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="17" t="n">
         <f aca="false">D13+D19</f>
         <v>112999.7</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="17" t="n">
         <f aca="false">E13+E19</f>
         <v>5543</v>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="17" t="n">
         <f aca="false">F13+F19</f>
         <v>118542.7</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G20" s="18" t="n">
         <f aca="false">IFERROR(F20/C20,"")</f>
         <v>0.342101739328683</v>
       </c>
-      <c r="H20" s="18" t="n">
+      <c r="H20" s="17" t="n">
         <f aca="false">IF(C20="","",C20-F20)</f>
         <v>227970.3</v>
       </c>
-      <c r="I20" s="18" t="n">
+      <c r="I20" s="17" t="n">
         <f aca="false">IFERROR((F20/$B$7)*$B$6,"")</f>
         <v>260793.94</v>
       </c>
-      <c r="J20" s="19" t="n">
+      <c r="J20" s="18" t="n">
         <f aca="false">IFERROR(I20/C20,"")</f>
         <v>0.752623826523103</v>
       </c>
@@ -1544,28 +1545,28 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="21"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6"/>
@@ -1580,10 +1581,10 @@
       <c r="J23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="24" t="n">
+      <c r="B24" s="23" t="n">
         <f aca="false">B7</f>
         <v>10</v>
       </c>
@@ -1597,10 +1598,10 @@
       <c r="J24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="25" t="n">
+      <c r="B25" s="24" t="n">
         <f aca="false">IFERROR(F20/B7,"—")</f>
         <v>11854.27</v>
       </c>
@@ -1614,25 +1615,25 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="27" t="n">
+      <c r="B26" s="26" t="n">
         <f aca="false">J20</f>
         <v>0.752623826523103</v>
       </c>
       <c r="C26" s="6"/>
-      <c r="D26" s="20"/>
+      <c r="D26" s="19"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
-      <c r="G26" s="28"/>
+      <c r="G26" s="27"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29"/>
-      <c r="B27" s="29"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="28"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -1643,10 +1644,10 @@
       <c r="J27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="31"/>
+      <c r="B28" s="30"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
@@ -1657,19 +1658,19 @@
       <c r="J28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="24" t="n">
+      <c r="B29" s="23" t="n">
         <f aca="false">IFERROR(B6-B7,"—")</f>
         <v>12</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="25" t="n">
+      <c r="B30" s="24" t="n">
         <f aca="false">IFERROR(H20/(B6-B7),"—")</f>
         <v>18997.525</v>
       </c>
@@ -1750,7 +1751,7 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32" t="n">
+      <c r="B2" s="31" t="n">
         <v>46250</v>
       </c>
     </row>
@@ -1766,7 +1767,7 @@
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="32" t="n">
+      <c r="B4" s="31" t="n">
         <f aca="false">EOMONTH(B3,-1)+1</f>
         <v>46235</v>
       </c>
@@ -1775,7 +1776,7 @@
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="32" t="n">
+      <c r="B5" s="31" t="n">
         <f aca="false">EOMONTH(B3,0)</f>
         <v>46265</v>
       </c>
@@ -1799,32 +1800,32 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
@@ -1865,13 +1866,13 @@
       <c r="B11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="34" t="n">
         <v>45780</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="34" t="n">
         <v>28518.9</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="34" t="n">
         <v>885</v>
       </c>
       <c r="F11" s="11" t="n">
@@ -1900,13 +1901,13 @@
       <c r="B12" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="35" t="n">
+      <c r="C12" s="34" t="n">
         <v>25070</v>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D12" s="34" t="n">
         <v>5330.1</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="34" t="n">
         <v>320</v>
       </c>
       <c r="F12" s="11" t="n">
@@ -1935,13 +1936,13 @@
       <c r="B13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="34" t="n">
         <v>167860</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="34" t="n">
         <v>78350.3</v>
       </c>
-      <c r="E13" s="36"/>
+      <c r="E13" s="35"/>
       <c r="F13" s="11" t="n">
         <f aca="false">D13+E13</f>
         <v>78350.3</v>
@@ -2006,13 +2007,13 @@
       <c r="B15" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="34" t="n">
         <v>28992</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="34" t="n">
         <v>8622</v>
       </c>
-      <c r="E15" s="36"/>
+      <c r="E15" s="35"/>
       <c r="F15" s="11" t="n">
         <f aca="false">D15+E15</f>
         <v>8622</v>
@@ -2040,10 +2041,10 @@
         <v>23</v>
       </c>
       <c r="C16" s="10"/>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="36"/>
+      <c r="E16" s="35"/>
       <c r="F16" s="11" t="n">
         <f aca="false">D16+E16</f>
         <v>0</v>
@@ -2070,13 +2071,13 @@
       <c r="B17" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="34" t="n">
         <v>43600</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="34" t="n">
         <v>27849.1</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="34" t="n">
         <v>2240</v>
       </c>
       <c r="F17" s="11" t="n">
@@ -2105,13 +2106,13 @@
       <c r="B18" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="35" t="n">
+      <c r="C18" s="34" t="n">
         <v>6250</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="36"/>
+      <c r="E18" s="35"/>
       <c r="F18" s="11" t="n">
         <f aca="false">D18+E18</f>
         <v>0</v>
@@ -2139,10 +2140,10 @@
         <v>26</v>
       </c>
       <c r="C19" s="10"/>
-      <c r="D19" s="35" t="n">
+      <c r="D19" s="34" t="n">
         <v>457</v>
       </c>
-      <c r="E19" s="36"/>
+      <c r="E19" s="35"/>
       <c r="F19" s="11" t="n">
         <f aca="false">D19+E19</f>
         <v>457</v>
@@ -2165,7 +2166,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="13" t="s">
         <v>21</v>
       </c>
@@ -2204,55 +2205,55 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="37"/>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="18" t="n">
+      <c r="C21" s="17" t="n">
         <f aca="false">C14+C20</f>
         <v>317552</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="17" t="n">
         <f aca="false">D14+D20</f>
         <v>149127.4</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="17" t="n">
         <f aca="false">E14+E20</f>
         <v>3445</v>
       </c>
-      <c r="F21" s="18" t="n">
+      <c r="F21" s="17" t="n">
         <f aca="false">F14+F20</f>
         <v>152572.4</v>
       </c>
-      <c r="G21" s="19" t="n">
+      <c r="G21" s="18" t="n">
         <f aca="false">IFERROR(F21/C21,"")</f>
         <v>0.480464301909609</v>
       </c>
-      <c r="H21" s="18" t="n">
+      <c r="H21" s="17" t="n">
         <f aca="false">IF(C21="","",C21-F21)</f>
         <v>164979.6</v>
       </c>
-      <c r="I21" s="18" t="n">
+      <c r="I21" s="17" t="n">
         <f aca="false">IFERROR((F21/$B$7)*$B$6,"")</f>
         <v>335659.28</v>
       </c>
-      <c r="J21" s="19" t="n">
+      <c r="J21" s="18" t="n">
         <f aca="false">IFERROR(I21/C21,"")</f>
         <v>1.05702146420114</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
     </row>
     <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2381,7 +2382,7 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32" t="n">
+      <c r="B2" s="31" t="n">
         <v>46250</v>
       </c>
     </row>
@@ -2397,7 +2398,7 @@
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="32" t="n">
+      <c r="B4" s="31" t="n">
         <f aca="false">EOMONTH(B3,-1)+1</f>
         <v>46235</v>
       </c>
@@ -2406,7 +2407,7 @@
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="32" t="n">
+      <c r="B5" s="31" t="n">
         <f aca="false">EOMONTH(B3,0)</f>
         <v>46265</v>
       </c>
@@ -2430,32 +2431,32 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
@@ -2496,13 +2497,13 @@
       <c r="B11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="34" t="n">
         <v>30520</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="34" t="n">
         <v>13592.7</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="34" t="n">
         <v>75</v>
       </c>
       <c r="F11" s="11" t="n">
@@ -2531,13 +2532,13 @@
       <c r="B12" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="35" t="n">
+      <c r="C12" s="34" t="n">
         <v>30520</v>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D12" s="34" t="n">
         <v>9861.2</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="34" t="n">
         <v>408</v>
       </c>
       <c r="F12" s="11" t="n">
@@ -2566,13 +2567,13 @@
       <c r="B13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="34" t="n">
         <v>161865</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="34" t="n">
         <v>64049.2</v>
       </c>
-      <c r="E13" s="36"/>
+      <c r="E13" s="35"/>
       <c r="F13" s="11" t="n">
         <f aca="false">D13+E13</f>
         <v>64049.2</v>
@@ -2637,13 +2638,13 @@
       <c r="B15" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="34" t="n">
         <v>12794</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="34" t="n">
         <v>4269</v>
       </c>
-      <c r="E15" s="36"/>
+      <c r="E15" s="35"/>
       <c r="F15" s="11" t="n">
         <f aca="false">D15+E15</f>
         <v>4269</v>
@@ -2670,13 +2671,13 @@
       <c r="B16" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="35" t="n">
+      <c r="C16" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="36"/>
+      <c r="E16" s="35"/>
       <c r="F16" s="11" t="n">
         <f aca="false">D16+E16</f>
         <v>0</v>
@@ -2703,13 +2704,13 @@
       <c r="B17" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="34" t="n">
         <v>6625</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="34" t="n">
         <v>4045</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="34" t="n">
         <v>537</v>
       </c>
       <c r="F17" s="11" t="n">
@@ -2738,13 +2739,13 @@
       <c r="B18" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="35" t="n">
+      <c r="C18" s="34" t="n">
         <v>22036</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="34" t="n">
         <v>1212</v>
       </c>
-      <c r="E18" s="36"/>
+      <c r="E18" s="35"/>
       <c r="F18" s="11" t="n">
         <f aca="false">D18+E18</f>
         <v>1212</v>
@@ -2772,8 +2773,8 @@
         <v>26</v>
       </c>
       <c r="C19" s="10"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="36"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
       <c r="F19" s="11" t="n">
         <f aca="false">D19+E19</f>
         <v>0</v>
@@ -2796,7 +2797,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="13" t="s">
         <v>21</v>
       </c>
@@ -2835,55 +2836,55 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="37"/>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="18" t="n">
+      <c r="C21" s="17" t="n">
         <f aca="false">C14+C20</f>
         <v>264360</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="17" t="n">
         <f aca="false">D14+D20</f>
         <v>97029.1</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="17" t="n">
         <f aca="false">E14+E20</f>
         <v>1020</v>
       </c>
-      <c r="F21" s="18" t="n">
+      <c r="F21" s="17" t="n">
         <f aca="false">F14+F20</f>
         <v>98049.1</v>
       </c>
-      <c r="G21" s="19" t="n">
+      <c r="G21" s="18" t="n">
         <f aca="false">IFERROR(F21/C21,"")</f>
         <v>0.370892343773642</v>
       </c>
-      <c r="H21" s="18" t="n">
+      <c r="H21" s="17" t="n">
         <f aca="false">IF(C21="","",C21-F21)</f>
         <v>166310.9</v>
       </c>
-      <c r="I21" s="18" t="n">
+      <c r="I21" s="17" t="n">
         <f aca="false">IFERROR((F21/$B$7)*$B$6,"")</f>
         <v>215708.02</v>
       </c>
-      <c r="J21" s="19" t="n">
+      <c r="J21" s="18" t="n">
         <f aca="false">IFERROR(I21/C21,"")</f>
         <v>0.815963156302012</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
     </row>
     <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3012,7 +3013,7 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32" t="n">
+      <c r="B2" s="31" t="n">
         <v>46250</v>
       </c>
     </row>
@@ -3028,7 +3029,7 @@
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="32" t="n">
+      <c r="B4" s="31" t="n">
         <f aca="false">EOMONTH(B3,-1)+1</f>
         <v>46235</v>
       </c>
@@ -3037,7 +3038,7 @@
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="32" t="n">
+      <c r="B5" s="31" t="n">
         <f aca="false">EOMONTH(B3,0)</f>
         <v>46265</v>
       </c>
@@ -3061,32 +3062,32 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
@@ -3127,13 +3128,13 @@
       <c r="B11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="34" t="n">
         <v>32700</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="34" t="n">
         <v>10036.8</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="34" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
@@ -3162,13 +3163,13 @@
       <c r="B12" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="35" t="n">
+      <c r="C12" s="34" t="n">
         <v>28340</v>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D12" s="34" t="n">
         <v>11639.9</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="34" t="n">
         <v>481</v>
       </c>
       <c r="F12" s="11" t="n">
@@ -3197,13 +3198,13 @@
       <c r="B13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="34" t="n">
         <v>149875</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="34" t="n">
         <v>56289.2</v>
       </c>
-      <c r="E13" s="36"/>
+      <c r="E13" s="35"/>
       <c r="F13" s="11" t="n">
         <f aca="false">D13+E13</f>
         <v>56289.2</v>
@@ -3268,13 +3269,13 @@
       <c r="B15" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="34" t="n">
         <v>10756</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="34" t="n">
         <v>1222</v>
       </c>
-      <c r="E15" s="36"/>
+      <c r="E15" s="35"/>
       <c r="F15" s="11" t="n">
         <f aca="false">D15+E15</f>
         <v>1222</v>
@@ -3301,13 +3302,13 @@
       <c r="B16" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="35" t="n">
+      <c r="C16" s="34" t="n">
         <v>7964</v>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="34" t="n">
         <v>899</v>
       </c>
-      <c r="E16" s="36"/>
+      <c r="E16" s="35"/>
       <c r="F16" s="11" t="n">
         <f aca="false">D16+E16</f>
         <v>899</v>
@@ -3334,13 +3335,13 @@
       <c r="B17" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="34" t="n">
         <v>21564</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="34" t="n">
         <v>7584.6</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="34" t="n">
         <v>132</v>
       </c>
       <c r="F17" s="11" t="n">
@@ -3369,13 +3370,13 @@
       <c r="B18" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="35" t="n">
+      <c r="C18" s="34" t="n">
         <v>5875</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="34" t="n">
         <v>157</v>
       </c>
-      <c r="E18" s="36"/>
+      <c r="E18" s="35"/>
       <c r="F18" s="11" t="n">
         <f aca="false">D18+E18</f>
         <v>157</v>
@@ -3403,8 +3404,8 @@
         <v>26</v>
       </c>
       <c r="C19" s="10"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="36"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
       <c r="F19" s="11" t="n">
         <f aca="false">D19+E19</f>
         <v>0</v>
@@ -3427,7 +3428,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="13" t="s">
         <v>21</v>
       </c>
@@ -3466,55 +3467,55 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="37"/>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="18" t="n">
+      <c r="C21" s="17" t="n">
         <f aca="false">C14+C20</f>
         <v>257074</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="17" t="n">
         <f aca="false">D14+D20</f>
         <v>87828.5</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="17" t="n">
         <f aca="false">E14+E20</f>
         <v>613</v>
       </c>
-      <c r="F21" s="18" t="n">
+      <c r="F21" s="17" t="n">
         <f aca="false">F14+F20</f>
         <v>88441.5</v>
       </c>
-      <c r="G21" s="19" t="n">
+      <c r="G21" s="18" t="n">
         <f aca="false">IFERROR(F21/C21,"")</f>
         <v>0.34403129060115</v>
       </c>
-      <c r="H21" s="18" t="n">
+      <c r="H21" s="17" t="n">
         <f aca="false">IF(C21="","",C21-F21)</f>
         <v>168632.5</v>
       </c>
-      <c r="I21" s="18" t="n">
+      <c r="I21" s="17" t="n">
         <f aca="false">IFERROR((F21/$B$7)*$B$6,"")</f>
         <v>194571.3</v>
       </c>
-      <c r="J21" s="19" t="n">
+      <c r="J21" s="18" t="n">
         <f aca="false">IFERROR(I21/C21,"")</f>
         <v>0.75686883932253</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
     </row>
     <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/kirill/outputs/hazam-tracking-dashboard.xlsx
+++ b/kirill/outputs/hazam-tracking-dashboard.xlsx
@@ -358,7 +358,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -387,12 +387,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor rgb="FF63BE7B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999"/>
-        <bgColor rgb="FFCC99FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -475,219 +469,219 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -700,7 +694,37 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF8696B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB84"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF63BE7B"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -828,7 +852,7 @@
       <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFFEB84"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFD99694"/>
+      <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
@@ -1543,134 +1567,134 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="20"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="23" t="n">
+      <c r="B24" s="24" t="n">
         <f aca="false">B7</f>
         <v>10</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="24" t="n">
+      <c r="B25" s="25" t="n">
         <f aca="false">IFERROR(F20/B7,"—")</f>
         <v>11854.27</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="27" t="n">
         <f aca="false">J20</f>
         <v>0.752623826523103</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="28"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="29" t="s">
         <v>32</v>
       </c>
       <c r="B28" s="30"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="23" t="n">
+      <c r="B29" s="24" t="n">
         <f aca="false">IFERROR(B6-B7,"—")</f>
         <v>12</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="24" t="n">
+      <c r="B30" s="25" t="n">
         <f aca="false">IFERROR(H20/(B6-B7),"—")</f>
         <v>18997.525</v>
       </c>
@@ -1695,13 +1719,13 @@
   </mergeCells>
   <conditionalFormatting sqref="B26">
     <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>0.33</formula>
+      <formula>0.8</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>0.66</formula>
+      <formula>1</formula>
     </cfRule>
     <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>0.66</formula>
+      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2242,18 +2266,18 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2325,13 +2349,13 @@
     <mergeCell ref="A28:J28"/>
   </mergeCells>
   <conditionalFormatting sqref="G26">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0.33</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0.66</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0.66</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2873,18 +2897,18 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2956,13 +2980,13 @@
     <mergeCell ref="A28:J28"/>
   </mergeCells>
   <conditionalFormatting sqref="G26">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0.33</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0.66</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0.66</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3504,18 +3528,18 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3587,13 +3611,13 @@
     <mergeCell ref="A28:J28"/>
   </mergeCells>
   <conditionalFormatting sqref="G26">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0.33</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0.66</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0.66</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3847,24 +3871,24 @@
     <mergeCell ref="A12:G12"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D10">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0.33</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0.66</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0.66</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E10">
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0.8</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="cellIs" priority="6" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/kirill/outputs/hazam-tracking-dashboard.xlsx
+++ b/kirill/outputs/hazam-tracking-dashboard.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="55">
   <si>
     <t xml:space="preserve">מעקב ביצועי סוכן חאזם</t>
   </si>
@@ -144,18 +144,6 @@
   </si>
   <si>
     <t xml:space="preserve">סיכום ביצועים — סה"כ כללי (דודו)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ימים שנותרו (א'-ה', עד סוף החודש)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">יעד יומי נדרש להשלמה (₪)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">אחוז ביצוע נוכחי (מתוך היעד הכולל)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערה: "ימים שנותרו" = סה"כ ימי א'-ה' בחודש (B6) פחות ימי א'-ה' שעברו עד יום הבדיקה (B7). "יעד יומי נדרש" = הסכום שנותר להשלמת היעד הכללי (H21) חלקי הימים שנותרו. עיצוב מותנה על תא האחוז: אדום מתחת ל-33%, צהוב 33%-66%, ירוק מעל 66%.</t>
   </si>
   <si>
     <t xml:space="preserve">מעקב ביצועי סוכן חיים</t>
@@ -317,14 +305,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="18"/>
       <color rgb="FF000000"/>
@@ -353,6 +333,14 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -464,224 +452,208 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="51">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -694,7 +666,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -718,51 +690,6 @@
     <dxf>
       <font>
         <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF63BE7B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF9C0006"/>
-        <sz val="14"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF8696B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF9C6500"/>
-        <sz val="14"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB84"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF006100"/>
-        <sz val="14"/>
       </font>
       <fill>
         <patternFill>
@@ -1743,10 +1670,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
@@ -2279,84 +2206,146 @@
       <c r="I23" s="22"/>
       <c r="J23" s="22"/>
     </row>
-    <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-    </row>
-    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="38" t="n">
+    <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <f aca="false">B7</f>
+        <v>10</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="25" t="n">
+        <f aca="false">IFERROR(F21/B7,"—")</f>
+        <v>15257.24</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="27" t="n">
+        <f aca="false">J21</f>
+        <v>1.05702146420114</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="24" t="n">
         <f aca="false">IFERROR(B6-B7,"—")</f>
         <v>12</v>
       </c>
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="39" t="n">
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="25" t="n">
         <f aca="false">IFERROR(H21/(B6-B7),"—")</f>
         <v>13748.3</v>
       </c>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40" t="n">
-        <f aca="false">IFERROR((D21+E21)/C21,"—")</f>
-        <v>0.480464301909609</v>
-      </c>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-    </row>
-    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A11:A19"/>
     <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="A28:J28"/>
   </mergeCells>
-  <conditionalFormatting sqref="G26">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>0.33</formula>
+  <conditionalFormatting sqref="B27">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0.8</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>0.66</formula>
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
-      <formula>0.66</formula>
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2374,10 +2363,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
@@ -2390,7 +2379,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2456,7 +2445,7 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B8" s="32"/>
       <c r="C8" s="32"/>
@@ -2516,7 +2505,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>18</v>
@@ -2898,7 +2887,7 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -2910,84 +2899,146 @@
       <c r="I23" s="22"/>
       <c r="J23" s="22"/>
     </row>
-    <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-    </row>
-    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="38" t="n">
+    <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <f aca="false">B7</f>
+        <v>10</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="25" t="n">
+        <f aca="false">IFERROR(F21/B7,"—")</f>
+        <v>9804.91</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="27" t="n">
+        <f aca="false">J21</f>
+        <v>0.815963156302012</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="24" t="n">
         <f aca="false">IFERROR(B6-B7,"—")</f>
         <v>12</v>
       </c>
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="39" t="n">
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="25" t="n">
         <f aca="false">IFERROR(H21/(B6-B7),"—")</f>
         <v>13859.2416666667</v>
       </c>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40" t="n">
-        <f aca="false">IFERROR((D21+E21)/C21,"—")</f>
-        <v>0.370892343773642</v>
-      </c>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-    </row>
-    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A11:A19"/>
     <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="A28:J28"/>
   </mergeCells>
-  <conditionalFormatting sqref="G26">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>0.33</formula>
+  <conditionalFormatting sqref="B27">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0.8</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>0.66</formula>
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
-      <formula>0.66</formula>
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3005,10 +3056,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
@@ -3021,7 +3072,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3087,7 +3138,7 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B8" s="32"/>
       <c r="C8" s="32"/>
@@ -3147,7 +3198,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>18</v>
@@ -3529,7 +3580,7 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -3541,84 +3592,146 @@
       <c r="I23" s="22"/>
       <c r="J23" s="22"/>
     </row>
-    <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-    </row>
-    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="38" t="n">
+    <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <f aca="false">B7</f>
+        <v>10</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="25" t="n">
+        <f aca="false">IFERROR(F21/B7,"—")</f>
+        <v>8844.15</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="27" t="n">
+        <f aca="false">J21</f>
+        <v>0.75686883932253</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="24" t="n">
         <f aca="false">IFERROR(B6-B7,"—")</f>
         <v>12</v>
       </c>
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="39" t="n">
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="25" t="n">
         <f aca="false">IFERROR(H21/(B6-B7),"—")</f>
         <v>14052.7083333333</v>
       </c>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40" t="n">
-        <f aca="false">IFERROR((D21+E21)/C21,"—")</f>
-        <v>0.34403129060115</v>
-      </c>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-    </row>
-    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A11:A19"/>
     <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="A28:J28"/>
   </mergeCells>
-  <conditionalFormatting sqref="G26">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>0.33</formula>
+  <conditionalFormatting sqref="B27">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0.8</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>0.66</formula>
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
-      <formula>0.66</formula>
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3647,221 +3760,221 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
+      <c r="A1" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="43" t="str">
+      <c r="A2" s="39" t="str">
         <f aca="false">"תצוגת מרכז לכל הסוכנים — נכון לתאריך חישוב "&amp;TEXT(חאזם!B2,"dd/mm/yy")&amp;" | יום בדיקה: "&amp;TEXT(חאזם!B3,"dd/mm/yy")&amp;"  |  סך ימי א-ה בחודש: "&amp;חאזם!B6&amp;"  |  ימים שעברו: "&amp;חאזם!B7&amp;"  |  ימים שנותרו: "&amp;חאזם!A26</f>
         <v>תצוגת מרכז לכל הסוכנים — נכון לתאריך חישוב 16/08/26 | יום בדיקה: 15/08/26  |  סך ימי א-ה בחודש: 22  |  ימים שעברו: 10  |  ימים שנותרו: קצב (%)</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
     </row>
     <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+    </row>
+    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-    </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5" s="45" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="46" t="n">
+      <c r="A6" s="42" t="n">
         <f aca="false">חאזם!A11</f>
         <v>0</v>
       </c>
-      <c r="B6" s="47" t="n">
+      <c r="B6" s="43" t="n">
         <f aca="false">חאזם!C21</f>
         <v>0</v>
       </c>
-      <c r="C6" s="47" t="n">
+      <c r="C6" s="43" t="n">
         <f aca="false">חאזם!D21+חאזם!E21</f>
         <v>0</v>
       </c>
-      <c r="D6" s="48" t="n">
+      <c r="D6" s="44" t="n">
         <f aca="false">חאזם!G21</f>
         <v>0</v>
       </c>
-      <c r="E6" s="48" t="n">
+      <c r="E6" s="44" t="n">
         <f aca="false">חאזם!J21</f>
         <v>0</v>
       </c>
-      <c r="F6" s="49" t="str">
+      <c r="F6" s="45" t="str">
         <f aca="false">חאזם!A26</f>
         <v>קצב (%)</v>
       </c>
-      <c r="G6" s="47" t="n">
+      <c r="G6" s="43" t="n">
         <f aca="false">חאזם!D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="46" t="str">
+      <c r="A7" s="42" t="str">
         <f aca="false">דודו!A11</f>
         <v>דודו</v>
       </c>
-      <c r="B7" s="47" t="n">
+      <c r="B7" s="43" t="n">
         <f aca="false">דודו!C21</f>
         <v>317552</v>
       </c>
-      <c r="C7" s="47" t="n">
+      <c r="C7" s="43" t="n">
         <f aca="false">דודו!D21+דודו!E21</f>
         <v>152572.4</v>
       </c>
-      <c r="D7" s="48" t="n">
+      <c r="D7" s="44" t="n">
         <f aca="false">דודו!G21</f>
         <v>0.480464301909609</v>
       </c>
-      <c r="E7" s="48" t="n">
+      <c r="E7" s="44" t="n">
         <f aca="false">דודו!J21</f>
         <v>1.05702146420114</v>
       </c>
-      <c r="F7" s="49" t="n">
+      <c r="F7" s="45" t="str">
         <f aca="false">דודו!A26</f>
-        <v>12</v>
-      </c>
-      <c r="G7" s="47" t="n">
+        <v>ממוצע מכירות יומי (₪)</v>
+      </c>
+      <c r="G7" s="43" t="n">
         <f aca="false">דודו!D26</f>
-        <v>13748.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="46" t="str">
+      <c r="A8" s="42" t="str">
         <f aca="false">חיים!A11</f>
         <v>חיים</v>
       </c>
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="43" t="n">
         <f aca="false">חיים!C21</f>
         <v>264360</v>
       </c>
-      <c r="C8" s="47" t="n">
+      <c r="C8" s="43" t="n">
         <f aca="false">חיים!D21+חיים!E21</f>
         <v>98049.1</v>
       </c>
-      <c r="D8" s="48" t="n">
+      <c r="D8" s="44" t="n">
         <f aca="false">חיים!G21</f>
         <v>0.370892343773642</v>
       </c>
-      <c r="E8" s="48" t="n">
+      <c r="E8" s="44" t="n">
         <f aca="false">חיים!J21</f>
         <v>0.815963156302012</v>
       </c>
-      <c r="F8" s="49" t="n">
+      <c r="F8" s="45" t="str">
         <f aca="false">חיים!A26</f>
-        <v>12</v>
-      </c>
-      <c r="G8" s="47" t="n">
+        <v>ממוצע מכירות יומי (₪)</v>
+      </c>
+      <c r="G8" s="43" t="n">
         <f aca="false">חיים!D26</f>
-        <v>13859.2416666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="46" t="str">
+      <c r="A9" s="42" t="str">
         <f aca="false">סטאס!A11</f>
         <v>סטאס</v>
       </c>
-      <c r="B9" s="47" t="n">
+      <c r="B9" s="43" t="n">
         <f aca="false">סטאס!C21</f>
         <v>257074</v>
       </c>
-      <c r="C9" s="47" t="n">
+      <c r="C9" s="43" t="n">
         <f aca="false">סטאס!D21+סטאס!E21</f>
         <v>88441.5</v>
       </c>
-      <c r="D9" s="48" t="n">
+      <c r="D9" s="44" t="n">
         <f aca="false">סטאס!G21</f>
         <v>0.34403129060115</v>
       </c>
-      <c r="E9" s="48" t="n">
+      <c r="E9" s="44" t="n">
         <f aca="false">סטאס!J21</f>
         <v>0.75686883932253</v>
       </c>
-      <c r="F9" s="49" t="n">
+      <c r="F9" s="45" t="str">
         <f aca="false">סטאס!A26</f>
-        <v>12</v>
-      </c>
-      <c r="G9" s="47" t="n">
+        <v>ממוצע מכירות יומי (₪)</v>
+      </c>
+      <c r="G9" s="43" t="n">
         <f aca="false">סטאס!D26</f>
-        <v>14052.7083333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="51" t="n">
+      <c r="B10" s="47" t="n">
         <f aca="false">SUM(B6:B9)</f>
         <v>838986</v>
       </c>
-      <c r="C10" s="51" t="n">
+      <c r="C10" s="47" t="n">
         <f aca="false">SUM(C6:C9)</f>
         <v>339063</v>
       </c>
-      <c r="D10" s="52" t="n">
+      <c r="D10" s="48" t="n">
         <f aca="false">IFERROR(C10/B10,"")</f>
         <v>0.404134276376483</v>
       </c>
-      <c r="E10" s="52" t="n">
+      <c r="E10" s="48" t="n">
         <f aca="false">IFERROR((חאזם!I21+דודו!I21+חיים!I21+סטאס!I21)/B10,"")</f>
         <v>0.889095408028263</v>
       </c>
-      <c r="F10" s="53" t="str">
+      <c r="F10" s="49" t="str">
         <f aca="false">F6</f>
         <v>קצב (%)</v>
       </c>
-      <c r="G10" s="51" t="str">
+      <c r="G10" s="47" t="str">
         <f aca="false">IFERROR((B10-C10)/F10,"")</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
+      <c r="A12" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3871,24 +3984,24 @@
     <mergeCell ref="A12:G12"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D10">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0.33</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0.66</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0.66</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E10">
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0.8</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" priority="6" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
